--- a/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{789ADFF8-066D-4A61-8BA6-83EF99E5DE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F419421F-CCC0-4958-9834-B1CE20168315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3361,7 +3361,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B30D215-4E0A-4A5E-BC8B-2557842FFD65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834FEDC3-7D6C-4396-9510-EF1B8FAF8DFB}">
   <dimension ref="B9:H169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19606,7 +19606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5E2CA4-D52F-4B08-925A-DD06F1903742}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AB0CAE-315A-4F19-935E-D4E6A80B7911}">
   <dimension ref="B9:L169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F419421F-CCC0-4958-9834-B1CE20168315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A4BE810-F055-4AEC-B65E-EFC9C7A972D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5221" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5333" uniqueCount="928">
   <si>
     <t>Unit</t>
   </si>
@@ -1396,367 +1396,415 @@
     <t>grid_node</t>
   </si>
   <si>
-    <t>p_w24394891_ARE</t>
-  </si>
-  <si>
-    <t>p_w29494113_ARE</t>
-  </si>
-  <si>
-    <t>p_w29495157_ARE</t>
-  </si>
-  <si>
-    <t>p_w29495366_ARE</t>
-  </si>
-  <si>
-    <t>p_w29497443_ARE</t>
-  </si>
-  <si>
-    <t>p_w29503687_ARE</t>
-  </si>
-  <si>
-    <t>p_w29504119_ARE</t>
-  </si>
-  <si>
-    <t>p_w29504133_ARE</t>
-  </si>
-  <si>
-    <t>p_w94816851_ARE</t>
-  </si>
-  <si>
-    <t>p_w94950807_ARE</t>
-  </si>
-  <si>
-    <t>p_w94950821_ARE</t>
-  </si>
-  <si>
-    <t>p_w94950847_ARE</t>
-  </si>
-  <si>
-    <t>p_w95046328_ARE</t>
-  </si>
-  <si>
-    <t>p_w95046332_ARE</t>
-  </si>
-  <si>
-    <t>p_w95046953_ARE</t>
-  </si>
-  <si>
-    <t>p_w95046964_ARE</t>
-  </si>
-  <si>
-    <t>p_w95055625_ARE</t>
-  </si>
-  <si>
-    <t>p_w95084771_ARE</t>
-  </si>
-  <si>
-    <t>p_w95084776_ARE</t>
-  </si>
-  <si>
-    <t>p_w95084793_ARE</t>
-  </si>
-  <si>
-    <t>p_w95084794_ARE</t>
-  </si>
-  <si>
-    <t>p_w95084799_ARE</t>
-  </si>
-  <si>
-    <t>p_w95084816_ARE</t>
-  </si>
-  <si>
-    <t>p_w1264942732_ARE</t>
-  </si>
-  <si>
-    <t>p_w95099964_ARE</t>
-  </si>
-  <si>
-    <t>p_w95099973_ARE</t>
-  </si>
-  <si>
-    <t>p_w301647038_ARE</t>
-  </si>
-  <si>
-    <t>p_w132159924_ARE</t>
-  </si>
-  <si>
-    <t>p_w132159930_ARE</t>
-  </si>
-  <si>
-    <t>p_w132517028_ARE</t>
-  </si>
-  <si>
-    <t>p_w149865727_ARE</t>
-  </si>
-  <si>
-    <t>p_w173064712_ARE</t>
-  </si>
-  <si>
-    <t>p_w174871442_ARE</t>
-  </si>
-  <si>
-    <t>p_w181332757_ARE</t>
-  </si>
-  <si>
-    <t>p_w181332762_ARE</t>
-  </si>
-  <si>
-    <t>p_w181332765_ARE</t>
-  </si>
-  <si>
-    <t>p_w181353369_ARE</t>
-  </si>
-  <si>
-    <t>p_w181353370_ARE</t>
-  </si>
-  <si>
-    <t>p_w181353393_ARE</t>
-  </si>
-  <si>
-    <t>p_w181361589_ARE</t>
-  </si>
-  <si>
-    <t>p_w181362976_ARE</t>
-  </si>
-  <si>
-    <t>p_w200057688_ARE</t>
-  </si>
-  <si>
-    <t>p_w1225551111_ARE</t>
-  </si>
-  <si>
-    <t>p_w227922802_ARE</t>
-  </si>
-  <si>
-    <t>p_w259874704_ARE</t>
-  </si>
-  <si>
-    <t>p_w260963603_ARE</t>
-  </si>
-  <si>
-    <t>p_w301651304_ARE</t>
-  </si>
-  <si>
-    <t>p_w301663552_ARE</t>
-  </si>
-  <si>
-    <t>p_w301663553_ARE</t>
-  </si>
-  <si>
-    <t>p_w301690692_ARE</t>
-  </si>
-  <si>
-    <t>p_w301715569_ARE</t>
-  </si>
-  <si>
-    <t>p_w301911494_ARE</t>
-  </si>
-  <si>
-    <t>p_w309146009_ARE</t>
-  </si>
-  <si>
-    <t>p_w354337246_ARE</t>
-  </si>
-  <si>
-    <t>p_w354337254_ARE</t>
-  </si>
-  <si>
-    <t>p_w354339381_ARE</t>
-  </si>
-  <si>
-    <t>p_w359425700_ARE</t>
-  </si>
-  <si>
-    <t>p_w375827318_ARE</t>
-  </si>
-  <si>
-    <t>p_w385901993_ARE</t>
-  </si>
-  <si>
-    <t>p_w395805805_ARE</t>
-  </si>
-  <si>
-    <t>p_w416954887_ARE</t>
-  </si>
-  <si>
-    <t>p_w416954890_ARE</t>
-  </si>
-  <si>
-    <t>p_w416981962_ARE</t>
-  </si>
-  <si>
-    <t>p_w438419245_ARE</t>
-  </si>
-  <si>
-    <t>p_w1264993337_ARE</t>
-  </si>
-  <si>
-    <t>p_w526194855_ARE</t>
-  </si>
-  <si>
-    <t>p_w722968894_ARE</t>
-  </si>
-  <si>
-    <t>p_w801739686_ARE</t>
-  </si>
-  <si>
-    <t>p_w900165939_ARE</t>
-  </si>
-  <si>
-    <t>p_w939814405_ARE</t>
-  </si>
-  <si>
-    <t>p_w1078341293_ARE</t>
-  </si>
-  <si>
-    <t>p_w1168317384_ARE</t>
-  </si>
-  <si>
-    <t>p_w1168317387_ARE</t>
-  </si>
-  <si>
-    <t>p_w1225109215_ARE</t>
-  </si>
-  <si>
-    <t>p_w1242347420_ARE</t>
-  </si>
-  <si>
-    <t>p_w1255406048_ARE</t>
-  </si>
-  <si>
-    <t>p_w1264973879_ARE</t>
-  </si>
-  <si>
-    <t>p_w1348312852_ARE</t>
-  </si>
-  <si>
-    <t>p_w1366982708_ARE</t>
-  </si>
-  <si>
-    <t>p_w1366988951_ARE</t>
-  </si>
-  <si>
-    <t>p_AE5_ARE</t>
-  </si>
-  <si>
-    <t>p_AE6_ARE</t>
-  </si>
-  <si>
-    <t>p_AE4_ARE</t>
-  </si>
-  <si>
-    <t>p_AE3_ARE</t>
-  </si>
-  <si>
-    <t>p_AE23_ARE</t>
-  </si>
-  <si>
-    <t>p_AE39_ARE</t>
-  </si>
-  <si>
-    <t>p_AE33_ARE</t>
-  </si>
-  <si>
-    <t>p_AE8_ARE</t>
-  </si>
-  <si>
-    <t>p_AE29_ARE</t>
-  </si>
-  <si>
-    <t>p_AE37_ARE</t>
-  </si>
-  <si>
-    <t>p_AE31_ARE</t>
-  </si>
-  <si>
-    <t>p_AE41_ARE</t>
-  </si>
-  <si>
-    <t>p_AE36_ARE</t>
-  </si>
-  <si>
-    <t>p_AE35_ARE</t>
-  </si>
-  <si>
-    <t>p_AE10_ARE</t>
-  </si>
-  <si>
-    <t>p_AE22_ARE</t>
-  </si>
-  <si>
-    <t>p_AE42_ARE</t>
-  </si>
-  <si>
-    <t>p_AE30_ARE</t>
-  </si>
-  <si>
-    <t>p_AE19_ARE</t>
-  </si>
-  <si>
-    <t>p_AE40_ARE</t>
-  </si>
-  <si>
-    <t>p_AE13_ARE</t>
-  </si>
-  <si>
-    <t>p_AE2_ARE</t>
-  </si>
-  <si>
-    <t>p_AE12_ARE</t>
-  </si>
-  <si>
-    <t>p_AE38_ARE</t>
-  </si>
-  <si>
-    <t>p_AE11_ARE</t>
-  </si>
-  <si>
-    <t>p_AE7_ARE</t>
-  </si>
-  <si>
-    <t>p_AE21_ARE</t>
-  </si>
-  <si>
-    <t>p_AE24_ARE</t>
-  </si>
-  <si>
-    <t>p_AE25_ARE</t>
-  </si>
-  <si>
-    <t>p_AE28_ARE</t>
-  </si>
-  <si>
-    <t>p_AE26_ARE</t>
-  </si>
-  <si>
-    <t>p_AE18_ARE</t>
-  </si>
-  <si>
-    <t>p_AE27_ARE</t>
-  </si>
-  <si>
-    <t>p_AE1_ARE</t>
-  </si>
-  <si>
-    <t>p_AE14_ARE</t>
-  </si>
-  <si>
-    <t>p_AE17_ARE</t>
-  </si>
-  <si>
-    <t>p_AE34_ARE</t>
-  </si>
-  <si>
-    <t>p_AE32_ARE</t>
-  </si>
-  <si>
-    <t>p_AE20_ARE</t>
-  </si>
-  <si>
-    <t>p_AE15_ARE</t>
-  </si>
-  <si>
-    <t>p_AE9_ARE</t>
+    <t>p_w24394891-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w24394891-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w29494113-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w29495157-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w29495366-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w29497443-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w29503687-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w29504119-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w29504119-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w29504133-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w94816851-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w94950807-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w94950821-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w94950847-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w95046328-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95046332-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95046953-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w95046953-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95046964-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95055625-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084771-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084776-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084793-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084794-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084799-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084799-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95084816-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w1264942732-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95099964-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w95099964-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w95099973-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w301647038-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w301647038-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w132159924-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w132159930-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w132517028-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w149865727-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w173064712-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w174871442-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w181332757-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w181332762-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w181332765-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w181353369-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w181353370-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w181353393-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w181361589-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w181362976-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w200057688-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w200057688-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w1225551111-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w227922802-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w259874704-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w259874704-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w260963603-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w301651304-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w301663552-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w301663553-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w301690692-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w301715569-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w301911494-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w309146009-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w354337246-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w354337254-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w354337254-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w354339381-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w359425700-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w375827318-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w385901993-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w395805805-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w416954887-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w416954890-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w416981962-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w438419245-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1264993337-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w526194855-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w722968894-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w801739686-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w900165939-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w939814405-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w1078341293-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1168317384-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w1168317387-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w1225109215-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1242347420-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1255406048-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1264973879-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w526194855-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1348312852-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1366982708-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1366988951-400_ARE</t>
+  </si>
+  <si>
+    <t>p_w1366988951-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE5-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE6-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE4-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE3-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE23-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE39-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE33-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE8-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE29-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE37-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE33-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE31-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE41-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE36-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE35-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE10-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE22-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE42-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE30-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE19-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE40-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE13-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE2-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE12-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE38-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE11-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE7-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE21-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE24-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE25-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE28-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE26-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE29-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE19-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE18-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE27-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE1-220_ARE</t>
+  </si>
+  <si>
+    <t>p_w354339381-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE14-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE17-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE18-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE34-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE32-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE20-220_ARE</t>
+  </si>
+  <si>
+    <t>p_AE15-400_ARE</t>
+  </si>
+  <si>
+    <t>p_AE9-400_ARE</t>
   </si>
   <si>
     <t>rez_spv_ARE_001</t>
@@ -3361,16 +3409,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834FEDC3-7D6C-4396-9510-EF1B8FAF8DFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3178FF-8CED-46E8-9658-1BE80596FCC5}">
   <dimension ref="B9:H169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
       <c r="F9" t="s">
-        <v>750</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" spans="2:8">
@@ -3378,19 +3426,19 @@
         <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="D10" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="F10" t="s">
         <v>429</v>
       </c>
       <c r="G10" t="s">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="H10" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -3404,7 +3452,7 @@
         <v>54.749784680955919</v>
       </c>
       <c r="F11" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="G11">
         <v>24.547972663038003</v>
@@ -3418,13 +3466,13 @@
         <v>438</v>
       </c>
       <c r="C12">
-        <v>25.231875294138504</v>
+        <v>24.547917124380174</v>
       </c>
       <c r="D12">
-        <v>55.407353887529432</v>
+        <v>54.749508681190633</v>
       </c>
       <c r="F12" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="G12">
         <v>24.547917124380174</v>
@@ -3438,13 +3486,13 @@
         <v>439</v>
       </c>
       <c r="C13">
-        <v>25.139845155997939</v>
+        <v>25.231875294138504</v>
       </c>
       <c r="D13">
-        <v>55.264331581825438</v>
+        <v>55.407353887529432</v>
       </c>
       <c r="F13" t="s">
-        <v>755</v>
+        <v>771</v>
       </c>
       <c r="G13">
         <v>25.231875294138504</v>
@@ -3458,13 +3506,13 @@
         <v>440</v>
       </c>
       <c r="C14">
-        <v>25.184555796553362</v>
+        <v>25.139845155997939</v>
       </c>
       <c r="D14">
-        <v>55.303483938756621</v>
+        <v>55.264331581825438</v>
       </c>
       <c r="F14" t="s">
-        <v>756</v>
+        <v>772</v>
       </c>
       <c r="G14">
         <v>25.139845155997939</v>
@@ -3478,13 +3526,13 @@
         <v>441</v>
       </c>
       <c r="C15">
-        <v>25.055382849547147</v>
+        <v>25.184555796553362</v>
       </c>
       <c r="D15">
-        <v>55.116557980654193</v>
+        <v>55.303483938756621</v>
       </c>
       <c r="F15" t="s">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="G15">
         <v>25.184555796553362</v>
@@ -3498,13 +3546,13 @@
         <v>442</v>
       </c>
       <c r="C16">
-        <v>24.348093372435439</v>
+        <v>25.055382849547147</v>
       </c>
       <c r="D16">
-        <v>54.59273997467016</v>
+        <v>55.116557980654193</v>
       </c>
       <c r="F16" t="s">
-        <v>758</v>
+        <v>774</v>
       </c>
       <c r="G16">
         <v>25.055382849547147</v>
@@ -3518,13 +3566,13 @@
         <v>443</v>
       </c>
       <c r="C17">
-        <v>24.291195799765124</v>
+        <v>24.348093372435439</v>
       </c>
       <c r="D17">
-        <v>54.54134261131388</v>
+        <v>54.59273997467016</v>
       </c>
       <c r="F17" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="G17">
         <v>24.348093372435439</v>
@@ -3538,13 +3586,13 @@
         <v>444</v>
       </c>
       <c r="C18">
-        <v>24.293704705896776</v>
+        <v>24.291195799765124</v>
       </c>
       <c r="D18">
-        <v>54.661224446708232</v>
+        <v>54.54134261131388</v>
       </c>
       <c r="F18" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="G18">
         <v>24.291195799765124</v>
@@ -3558,13 +3606,13 @@
         <v>445</v>
       </c>
       <c r="C19">
-        <v>25.749414303083199</v>
+        <v>24.291139258425524</v>
       </c>
       <c r="D19">
-        <v>55.98012577789671</v>
+        <v>54.541067728273887</v>
       </c>
       <c r="F19" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
       <c r="G19">
         <v>24.291139258425524</v>
@@ -3578,13 +3626,13 @@
         <v>446</v>
       </c>
       <c r="C20">
-        <v>24.442985561944049</v>
+        <v>24.293704705896776</v>
       </c>
       <c r="D20">
-        <v>54.479060321670318</v>
+        <v>54.661224446708232</v>
       </c>
       <c r="F20" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="G20">
         <v>24.293704705896776</v>
@@ -3598,13 +3646,13 @@
         <v>447</v>
       </c>
       <c r="C21">
-        <v>24.763961828391281</v>
+        <v>25.749414303083199</v>
       </c>
       <c r="D21">
-        <v>54.691576102928266</v>
+        <v>55.98012577789671</v>
       </c>
       <c r="F21" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="G21">
         <v>25.749414303083199</v>
@@ -3618,13 +3666,13 @@
         <v>448</v>
       </c>
       <c r="C22">
-        <v>24.44452607858582</v>
+        <v>24.442985561944049</v>
       </c>
       <c r="D22">
-        <v>54.443717124990869</v>
+        <v>54.479060321670318</v>
       </c>
       <c r="F22" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="G22">
         <v>24.442985561944049</v>
@@ -3638,13 +3686,13 @@
         <v>449</v>
       </c>
       <c r="C23">
-        <v>24.750940192507869</v>
+        <v>24.763961828391281</v>
       </c>
       <c r="D23">
-        <v>54.852162280472669</v>
+        <v>54.691576102928266</v>
       </c>
       <c r="F23" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="G23">
         <v>24.763961828391281</v>
@@ -3658,13 +3706,13 @@
         <v>450</v>
       </c>
       <c r="C24">
-        <v>24.318460214644851</v>
+        <v>24.44452607858582</v>
       </c>
       <c r="D24">
-        <v>54.511228686081459</v>
+        <v>54.443717124990869</v>
       </c>
       <c r="F24" t="s">
-        <v>766</v>
+        <v>782</v>
       </c>
       <c r="G24">
         <v>24.44452607858582</v>
@@ -3678,13 +3726,13 @@
         <v>451</v>
       </c>
       <c r="C25">
-        <v>24.519494620993068</v>
+        <v>24.750940192507869</v>
       </c>
       <c r="D25">
-        <v>55.421780172819112</v>
+        <v>54.852162280472669</v>
       </c>
       <c r="F25" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="G25">
         <v>24.750940192507869</v>
@@ -3698,13 +3746,13 @@
         <v>452</v>
       </c>
       <c r="C26">
-        <v>24.174548473125199</v>
+        <v>24.318460214644851</v>
       </c>
       <c r="D26">
-        <v>55.097418303604819</v>
+        <v>54.511228686081459</v>
       </c>
       <c r="F26" t="s">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="G26">
         <v>24.318460214644851</v>
@@ -3718,13 +3766,13 @@
         <v>453</v>
       </c>
       <c r="C27">
-        <v>24.191776039650399</v>
+        <v>24.519494620993068</v>
       </c>
       <c r="D27">
-        <v>55.331721098244152</v>
+        <v>55.421780172819112</v>
       </c>
       <c r="F27" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="G27">
         <v>24.519494620993068</v>
@@ -3738,13 +3786,13 @@
         <v>454</v>
       </c>
       <c r="C28">
-        <v>24.165091441075383</v>
+        <v>24.519441663383411</v>
       </c>
       <c r="D28">
-        <v>55.773357510706163</v>
+        <v>55.421503465293732</v>
       </c>
       <c r="F28" t="s">
-        <v>770</v>
+        <v>786</v>
       </c>
       <c r="G28">
         <v>24.519441663383411</v>
@@ -3758,13 +3806,13 @@
         <v>455</v>
       </c>
       <c r="C29">
-        <v>24.573436185982629</v>
+        <v>24.174548473125199</v>
       </c>
       <c r="D29">
-        <v>55.729424550034047</v>
+        <v>55.097418303604819</v>
       </c>
       <c r="F29" t="s">
-        <v>771</v>
+        <v>787</v>
       </c>
       <c r="G29">
         <v>24.174548473125199</v>
@@ -3778,13 +3826,13 @@
         <v>456</v>
       </c>
       <c r="C30">
-        <v>24.189276932757242</v>
+        <v>24.191776039650399</v>
       </c>
       <c r="D30">
-        <v>55.695413037745432</v>
+        <v>55.331721098244152</v>
       </c>
       <c r="F30" t="s">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="G30">
         <v>24.191776039650399</v>
@@ -3798,13 +3846,13 @@
         <v>457</v>
       </c>
       <c r="C31">
-        <v>24.391309663218081</v>
+        <v>24.165091441075383</v>
       </c>
       <c r="D31">
-        <v>55.794268238587762</v>
+        <v>55.773357510706163</v>
       </c>
       <c r="F31" t="s">
-        <v>773</v>
+        <v>789</v>
       </c>
       <c r="G31">
         <v>24.165091441075383</v>
@@ -3818,13 +3866,13 @@
         <v>458</v>
       </c>
       <c r="C32">
-        <v>24.258485710257435</v>
+        <v>24.573436185982629</v>
       </c>
       <c r="D32">
-        <v>55.685483290883177</v>
+        <v>55.729424550034047</v>
       </c>
       <c r="F32" t="s">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="G32">
         <v>24.573436185982629</v>
@@ -3838,13 +3886,13 @@
         <v>459</v>
       </c>
       <c r="C33">
-        <v>24.230197217818457</v>
+        <v>24.189276932757242</v>
       </c>
       <c r="D33">
-        <v>55.573030236906149</v>
+        <v>55.695413037745432</v>
       </c>
       <c r="F33" t="s">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="G33">
         <v>24.189276932757242</v>
@@ -3858,13 +3906,13 @@
         <v>460</v>
       </c>
       <c r="C34">
-        <v>24.220792466388943</v>
+        <v>24.391309663218081</v>
       </c>
       <c r="D34">
-        <v>54.146956696162711</v>
+        <v>55.794268238587762</v>
       </c>
       <c r="F34" t="s">
-        <v>776</v>
+        <v>792</v>
       </c>
       <c r="G34">
         <v>24.391309663218081</v>
@@ -3878,13 +3926,13 @@
         <v>461</v>
       </c>
       <c r="C35">
-        <v>23.576973300265919</v>
+        <v>24.258485710257435</v>
       </c>
       <c r="D35">
-        <v>53.730224792983321</v>
+        <v>55.685483290883177</v>
       </c>
       <c r="F35" t="s">
-        <v>777</v>
+        <v>793</v>
       </c>
       <c r="G35">
         <v>24.258485710257435</v>
@@ -3898,13 +3946,13 @@
         <v>462</v>
       </c>
       <c r="C36">
-        <v>23.13009337430924</v>
+        <v>24.258433574388413</v>
       </c>
       <c r="D36">
-        <v>53.794361008007677</v>
+        <v>55.685207150162277</v>
       </c>
       <c r="F36" t="s">
-        <v>778</v>
+        <v>794</v>
       </c>
       <c r="G36">
         <v>24.258433574388413</v>
@@ -3918,13 +3966,13 @@
         <v>463</v>
       </c>
       <c r="C37">
-        <v>24.153522813685164</v>
+        <v>24.230197217818457</v>
       </c>
       <c r="D37">
-        <v>52.574021574090885</v>
+        <v>55.573030236906149</v>
       </c>
       <c r="F37" t="s">
-        <v>779</v>
+        <v>795</v>
       </c>
       <c r="G37">
         <v>24.230197217818457</v>
@@ -3938,13 +3986,13 @@
         <v>464</v>
       </c>
       <c r="C38">
-        <v>23.409693666120081</v>
+        <v>24.220792466388943</v>
       </c>
       <c r="D38">
-        <v>55.396902550407042</v>
+        <v>54.146956696162711</v>
       </c>
       <c r="F38" t="s">
-        <v>780</v>
+        <v>796</v>
       </c>
       <c r="G38">
         <v>24.220792466388943</v>
@@ -3958,13 +4006,13 @@
         <v>465</v>
       </c>
       <c r="C39">
-        <v>24.056917805666899</v>
+        <v>23.576973300265919</v>
       </c>
       <c r="D39">
-        <v>51.766616731764508</v>
+        <v>53.730224792983321</v>
       </c>
       <c r="F39" t="s">
-        <v>781</v>
+        <v>797</v>
       </c>
       <c r="G39">
         <v>23.576973300265919</v>
@@ -3978,13 +4026,13 @@
         <v>466</v>
       </c>
       <c r="C40">
-        <v>24.090419435849679</v>
+        <v>23.576913091785521</v>
       </c>
       <c r="D40">
-        <v>52.755360812337877</v>
+        <v>53.729953263945717</v>
       </c>
       <c r="F40" t="s">
-        <v>782</v>
+        <v>798</v>
       </c>
       <c r="G40">
         <v>23.576913091785521</v>
@@ -3998,13 +4046,13 @@
         <v>467</v>
       </c>
       <c r="C41">
-        <v>25.03646467988704</v>
+        <v>23.13009337430924</v>
       </c>
       <c r="D41">
-        <v>55.292655946621501</v>
+        <v>53.794361008007677</v>
       </c>
       <c r="F41" t="s">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="G41">
         <v>23.13009337430924</v>
@@ -4018,13 +4066,13 @@
         <v>468</v>
       </c>
       <c r="C42">
-        <v>25.010728893210121</v>
+        <v>24.153522813685164</v>
       </c>
       <c r="D42">
-        <v>55.169746030068957</v>
+        <v>52.574021574090885</v>
       </c>
       <c r="F42" t="s">
-        <v>784</v>
+        <v>800</v>
       </c>
       <c r="G42">
         <v>24.153522813685164</v>
@@ -4038,13 +4086,13 @@
         <v>469</v>
       </c>
       <c r="C43">
-        <v>24.497202420667879</v>
+        <v>24.153458643465228</v>
       </c>
       <c r="D43">
-        <v>54.471280256089152</v>
+        <v>52.573749570288861</v>
       </c>
       <c r="F43" t="s">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="G43">
         <v>24.153458643465228</v>
@@ -4058,13 +4106,13 @@
         <v>470</v>
       </c>
       <c r="C44">
-        <v>24.909908123344923</v>
+        <v>23.409693666120081</v>
       </c>
       <c r="D44">
-        <v>55.080014433080272</v>
+        <v>55.396902550407042</v>
       </c>
       <c r="F44" t="s">
-        <v>786</v>
+        <v>802</v>
       </c>
       <c r="G44">
         <v>23.409693666120081</v>
@@ -4078,13 +4126,13 @@
         <v>471</v>
       </c>
       <c r="C45">
-        <v>24.941396701754901</v>
+        <v>24.056917805666899</v>
       </c>
       <c r="D45">
-        <v>55.072014352841926</v>
+        <v>51.766616731764508</v>
       </c>
       <c r="F45" t="s">
-        <v>787</v>
+        <v>803</v>
       </c>
       <c r="G45">
         <v>24.056917805666899</v>
@@ -4098,13 +4146,13 @@
         <v>472</v>
       </c>
       <c r="C46">
-        <v>24.161696036259663</v>
+        <v>24.090419435849679</v>
       </c>
       <c r="D46">
-        <v>54.305206698058228</v>
+        <v>52.755360812337877</v>
       </c>
       <c r="F46" t="s">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="G46">
         <v>24.090419435849679</v>
@@ -4118,13 +4166,13 @@
         <v>473</v>
       </c>
       <c r="C47">
-        <v>23.851206279526803</v>
+        <v>25.03646467988704</v>
       </c>
       <c r="D47">
-        <v>53.626693192202573</v>
+        <v>55.292655946621501</v>
       </c>
       <c r="F47" t="s">
-        <v>789</v>
+        <v>805</v>
       </c>
       <c r="G47">
         <v>25.03646467988704</v>
@@ -4138,13 +4186,13 @@
         <v>474</v>
       </c>
       <c r="C48">
-        <v>23.546692358378351</v>
+        <v>25.010728893210121</v>
       </c>
       <c r="D48">
-        <v>53.303419571062967</v>
+        <v>55.169746030068957</v>
       </c>
       <c r="F48" t="s">
-        <v>790</v>
+        <v>806</v>
       </c>
       <c r="G48">
         <v>25.010728893210121</v>
@@ -4158,13 +4206,13 @@
         <v>475</v>
       </c>
       <c r="C49">
-        <v>23.833788124967644</v>
+        <v>24.497202420667879</v>
       </c>
       <c r="D49">
-        <v>53.648412191585777</v>
+        <v>54.471280256089152</v>
       </c>
       <c r="F49" t="s">
-        <v>791</v>
+        <v>807</v>
       </c>
       <c r="G49">
         <v>24.497202420667879</v>
@@ -4178,13 +4226,13 @@
         <v>476</v>
       </c>
       <c r="C50">
-        <v>23.290459929421743</v>
+        <v>24.909908123344923</v>
       </c>
       <c r="D50">
-        <v>54.232198131972332</v>
+        <v>55.080014433080272</v>
       </c>
       <c r="F50" t="s">
-        <v>792</v>
+        <v>808</v>
       </c>
       <c r="G50">
         <v>24.909908123344923</v>
@@ -4198,13 +4246,13 @@
         <v>477</v>
       </c>
       <c r="C51">
-        <v>24.111332505104642</v>
+        <v>24.941396701754901</v>
       </c>
       <c r="D51">
-        <v>55.821685153665392</v>
+        <v>55.072014352841926</v>
       </c>
       <c r="F51" t="s">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="G51">
         <v>24.941396701754901</v>
@@ -4218,13 +4266,13 @@
         <v>478</v>
       </c>
       <c r="C52">
-        <v>24.101509948228696</v>
+        <v>24.161696036259663</v>
       </c>
       <c r="D52">
-        <v>55.590266462916574</v>
+        <v>54.305206698058228</v>
       </c>
       <c r="F52" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="G52">
         <v>24.161696036259663</v>
@@ -4238,13 +4286,13 @@
         <v>479</v>
       </c>
       <c r="C53">
-        <v>24.069266464734881</v>
+        <v>23.851206279526803</v>
       </c>
       <c r="D53">
-        <v>54.323195825333478</v>
+        <v>53.626693192202573</v>
       </c>
       <c r="F53" t="s">
-        <v>795</v>
+        <v>811</v>
       </c>
       <c r="G53">
         <v>23.851206279526803</v>
@@ -4258,13 +4306,13 @@
         <v>480</v>
       </c>
       <c r="C54">
-        <v>23.320163165191779</v>
+        <v>23.546692358378351</v>
       </c>
       <c r="D54">
-        <v>54.173403944765148</v>
+        <v>53.303419571062967</v>
       </c>
       <c r="F54" t="s">
-        <v>796</v>
+        <v>812</v>
       </c>
       <c r="G54">
         <v>23.546692358378351</v>
@@ -4278,13 +4326,13 @@
         <v>481</v>
       </c>
       <c r="C55">
-        <v>24.279947799001249</v>
+        <v>23.833788124967644</v>
       </c>
       <c r="D55">
-        <v>54.488056326975808</v>
+        <v>53.648412191585777</v>
       </c>
       <c r="F55" t="s">
-        <v>797</v>
+        <v>813</v>
       </c>
       <c r="G55">
         <v>23.833788124967644</v>
@@ -4298,13 +4346,13 @@
         <v>482</v>
       </c>
       <c r="C56">
-        <v>25.152551289791258</v>
+        <v>23.290459929421743</v>
       </c>
       <c r="D56">
-        <v>56.28226729304189</v>
+        <v>54.232198131972332</v>
       </c>
       <c r="F56" t="s">
-        <v>798</v>
+        <v>814</v>
       </c>
       <c r="G56">
         <v>23.290459929421743</v>
@@ -4318,13 +4366,13 @@
         <v>483</v>
       </c>
       <c r="C57">
-        <v>24.082585485541681</v>
+        <v>24.111332505104642</v>
       </c>
       <c r="D57">
-        <v>52.721096532098478</v>
+        <v>55.821685153665392</v>
       </c>
       <c r="F57" t="s">
-        <v>799</v>
+        <v>815</v>
       </c>
       <c r="G57">
         <v>24.111332505104642</v>
@@ -4338,13 +4386,13 @@
         <v>484</v>
       </c>
       <c r="C58">
-        <v>22.783422386324691</v>
+        <v>24.101509948228696</v>
       </c>
       <c r="D58">
-        <v>54.718091249084502</v>
+        <v>55.590266462916574</v>
       </c>
       <c r="F58" t="s">
-        <v>800</v>
+        <v>816</v>
       </c>
       <c r="G58">
         <v>24.101509948228696</v>
@@ -4358,13 +4406,13 @@
         <v>485</v>
       </c>
       <c r="C59">
-        <v>23.700654787128688</v>
+        <v>24.101457319433603</v>
       </c>
       <c r="D59">
-        <v>52.917835349921631</v>
+        <v>55.589990960209931</v>
       </c>
       <c r="F59" t="s">
-        <v>801</v>
+        <v>817</v>
       </c>
       <c r="G59">
         <v>24.101457319433603</v>
@@ -4378,13 +4426,13 @@
         <v>486</v>
       </c>
       <c r="C60">
-        <v>24.103884184248937</v>
+        <v>24.069266464734881</v>
       </c>
       <c r="D60">
-        <v>53.426427579565463</v>
+        <v>54.323195825333478</v>
       </c>
       <c r="F60" t="s">
-        <v>802</v>
+        <v>818</v>
       </c>
       <c r="G60">
         <v>24.069266464734881</v>
@@ -4398,13 +4446,13 @@
         <v>487</v>
       </c>
       <c r="C61">
-        <v>23.34555865944559</v>
+        <v>23.320163165191779</v>
       </c>
       <c r="D61">
-        <v>54.146822717662616</v>
+        <v>54.173403944765148</v>
       </c>
       <c r="F61" t="s">
-        <v>803</v>
+        <v>819</v>
       </c>
       <c r="G61">
         <v>23.320163165191779</v>
@@ -4418,13 +4466,13 @@
         <v>488</v>
       </c>
       <c r="C62">
-        <v>25.302410283941761</v>
+        <v>24.279947799001249</v>
       </c>
       <c r="D62">
-        <v>56.369065495828721</v>
+        <v>54.488056326975808</v>
       </c>
       <c r="F62" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
       <c r="G62">
         <v>24.279947799001249</v>
@@ -4438,13 +4486,13 @@
         <v>489</v>
       </c>
       <c r="C63">
-        <v>24.094839420951168</v>
+        <v>24.279891043593281</v>
       </c>
       <c r="D63">
-        <v>51.638138014978217</v>
+        <v>54.487781546078281</v>
       </c>
       <c r="F63" t="s">
-        <v>805</v>
+        <v>821</v>
       </c>
       <c r="G63">
         <v>24.279891043593281</v>
@@ -4458,13 +4506,13 @@
         <v>490</v>
       </c>
       <c r="C64">
-        <v>22.916576275070149</v>
+        <v>25.152551289791258</v>
       </c>
       <c r="D64">
-        <v>53.962939772762745</v>
+        <v>56.28226729304189</v>
       </c>
       <c r="F64" t="s">
-        <v>806</v>
+        <v>822</v>
       </c>
       <c r="G64">
         <v>25.152551289791258</v>
@@ -4478,13 +4526,13 @@
         <v>491</v>
       </c>
       <c r="C65">
-        <v>23.731018140919726</v>
+        <v>24.082585485541681</v>
       </c>
       <c r="D65">
-        <v>53.486589579776023</v>
+        <v>52.721096532098478</v>
       </c>
       <c r="F65" t="s">
-        <v>807</v>
+        <v>823</v>
       </c>
       <c r="G65">
         <v>24.082585485541681</v>
@@ -4498,13 +4546,13 @@
         <v>492</v>
       </c>
       <c r="C66">
-        <v>25.370274138276137</v>
+        <v>22.783422386324691</v>
       </c>
       <c r="D66">
-        <v>55.466444796745307</v>
+        <v>54.718091249084502</v>
       </c>
       <c r="F66" t="s">
-        <v>808</v>
+        <v>824</v>
       </c>
       <c r="G66">
         <v>22.783422386324691</v>
@@ -4518,13 +4566,13 @@
         <v>493</v>
       </c>
       <c r="C67">
-        <v>25.066111288191728</v>
+        <v>23.700654787128688</v>
       </c>
       <c r="D67">
-        <v>55.19385071408982</v>
+        <v>52.917835349921631</v>
       </c>
       <c r="F67" t="s">
-        <v>809</v>
+        <v>825</v>
       </c>
       <c r="G67">
         <v>23.700654787128688</v>
@@ -4538,13 +4586,13 @@
         <v>494</v>
       </c>
       <c r="C68">
-        <v>25.174712739130531</v>
+        <v>24.103884184248937</v>
       </c>
       <c r="D68">
-        <v>55.38145984069773</v>
+        <v>53.426427579565463</v>
       </c>
       <c r="F68" t="s">
-        <v>810</v>
+        <v>826</v>
       </c>
       <c r="G68">
         <v>24.103884184248937</v>
@@ -4558,13 +4606,13 @@
         <v>495</v>
       </c>
       <c r="C69">
-        <v>25.170825392382472</v>
+        <v>23.34555865944559</v>
       </c>
       <c r="D69">
-        <v>55.33392177854919</v>
+        <v>54.146822717662616</v>
       </c>
       <c r="F69" t="s">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="G69">
         <v>23.34555865944559</v>
@@ -4578,13 +4626,13 @@
         <v>496</v>
       </c>
       <c r="C70">
-        <v>22.996693207288089</v>
+        <v>25.302410283941761</v>
       </c>
       <c r="D70">
-        <v>53.44115718974556</v>
+        <v>56.369065495828721</v>
       </c>
       <c r="F70" t="s">
-        <v>812</v>
+        <v>828</v>
       </c>
       <c r="G70">
         <v>25.302410283941761</v>
@@ -4598,13 +4646,13 @@
         <v>497</v>
       </c>
       <c r="C71">
-        <v>24.410018160478749</v>
+        <v>24.094839420951168</v>
       </c>
       <c r="D71">
-        <v>54.767609729242047</v>
+        <v>51.638138014978217</v>
       </c>
       <c r="F71" t="s">
-        <v>813</v>
+        <v>829</v>
       </c>
       <c r="G71">
         <v>24.094839420951168</v>
@@ -4618,13 +4666,13 @@
         <v>498</v>
       </c>
       <c r="C72">
-        <v>24.83751085990756</v>
+        <v>22.916576275070149</v>
       </c>
       <c r="D72">
-        <v>54.891148314936586</v>
+        <v>53.962939772762745</v>
       </c>
       <c r="F72" t="s">
-        <v>814</v>
+        <v>830</v>
       </c>
       <c r="G72">
         <v>22.916576275070149</v>
@@ -4638,13 +4686,13 @@
         <v>499</v>
       </c>
       <c r="C73">
-        <v>24.51384823571491</v>
+        <v>23.731018140919726</v>
       </c>
       <c r="D73">
-        <v>54.643350624212353</v>
+        <v>53.486589579776023</v>
       </c>
       <c r="F73" t="s">
-        <v>815</v>
+        <v>831</v>
       </c>
       <c r="G73">
         <v>23.731018140919726</v>
@@ -4658,13 +4706,13 @@
         <v>500</v>
       </c>
       <c r="C74">
-        <v>24.765320216216569</v>
+        <v>23.730957120400976</v>
       </c>
       <c r="D74">
-        <v>55.359019670921597</v>
+        <v>53.486317843564301</v>
       </c>
       <c r="F74" t="s">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="G74">
         <v>23.730957120400976</v>
@@ -4678,13 +4726,13 @@
         <v>501</v>
       </c>
       <c r="C75">
-        <v>23.965424841965429</v>
+        <v>25.370274138276137</v>
       </c>
       <c r="D75">
-        <v>52.232053362707831</v>
+        <v>55.466444796745307</v>
       </c>
       <c r="F75" t="s">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="G75">
         <v>25.370274138276137</v>
@@ -4698,13 +4746,13 @@
         <v>502</v>
       </c>
       <c r="C76">
-        <v>24.116823790882982</v>
+        <v>25.066111288191728</v>
       </c>
       <c r="D76">
-        <v>53.449772620070192</v>
+        <v>55.19385071408982</v>
       </c>
       <c r="F76" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="G76">
         <v>25.066111288191728</v>
@@ -4718,13 +4766,13 @@
         <v>503</v>
       </c>
       <c r="C77">
-        <v>24.902804802194161</v>
+        <v>25.174712739130531</v>
       </c>
       <c r="D77">
-        <v>54.931508517983445</v>
+        <v>55.38145984069773</v>
       </c>
       <c r="F77" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="G77">
         <v>25.174712739130531</v>
@@ -4738,13 +4786,13 @@
         <v>504</v>
       </c>
       <c r="C78">
-        <v>25.027949043595768</v>
+        <v>25.170825392382472</v>
       </c>
       <c r="D78">
-        <v>55.165057751776168</v>
+        <v>55.33392177854919</v>
       </c>
       <c r="F78" t="s">
-        <v>820</v>
+        <v>836</v>
       </c>
       <c r="G78">
         <v>25.170825392382472</v>
@@ -4758,13 +4806,13 @@
         <v>505</v>
       </c>
       <c r="C79">
-        <v>24.170593005635538</v>
+        <v>22.996693207288089</v>
       </c>
       <c r="D79">
-        <v>54.42668570728047</v>
+        <v>53.44115718974556</v>
       </c>
       <c r="F79" t="s">
-        <v>821</v>
+        <v>837</v>
       </c>
       <c r="G79">
         <v>22.996693207288089</v>
@@ -4778,13 +4826,13 @@
         <v>506</v>
       </c>
       <c r="C80">
-        <v>23.910974868997364</v>
+        <v>24.410018160478749</v>
       </c>
       <c r="D80">
-        <v>53.702691991144988</v>
+        <v>54.767609729242047</v>
       </c>
       <c r="F80" t="s">
-        <v>822</v>
+        <v>838</v>
       </c>
       <c r="G80">
         <v>24.410018160478749</v>
@@ -4798,13 +4846,13 @@
         <v>507</v>
       </c>
       <c r="C81">
-        <v>24.334856796200501</v>
+        <v>24.83751085990756</v>
       </c>
       <c r="D81">
-        <v>54.588781735586792</v>
+        <v>54.891148314936586</v>
       </c>
       <c r="F81" t="s">
-        <v>823</v>
+        <v>839</v>
       </c>
       <c r="G81">
         <v>24.83751085990756</v>
@@ -4818,13 +4866,13 @@
         <v>508</v>
       </c>
       <c r="C82">
-        <v>24.537581418017712</v>
+        <v>24.51384823571491</v>
       </c>
       <c r="D82">
-        <v>55.450638077281006</v>
+        <v>54.643350624212353</v>
       </c>
       <c r="F82" t="s">
-        <v>824</v>
+        <v>840</v>
       </c>
       <c r="G82">
         <v>24.51384823571491</v>
@@ -4838,13 +4886,13 @@
         <v>509</v>
       </c>
       <c r="C83">
-        <v>24.529944655230668</v>
+        <v>24.765320216216569</v>
       </c>
       <c r="D83">
-        <v>55.432484246499342</v>
+        <v>55.359019670921597</v>
       </c>
       <c r="F83" t="s">
-        <v>825</v>
+        <v>841</v>
       </c>
       <c r="G83">
         <v>24.765320216216569</v>
@@ -4858,13 +4906,13 @@
         <v>510</v>
       </c>
       <c r="C84">
-        <v>24.129711739367323</v>
+        <v>23.965424841965429</v>
       </c>
       <c r="D84">
-        <v>54.550975842015639</v>
+        <v>52.232053362707831</v>
       </c>
       <c r="F84" t="s">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="G84">
         <v>23.965424841965429</v>
@@ -4878,13 +4926,13 @@
         <v>511</v>
       </c>
       <c r="C85">
-        <v>24.769682128938115</v>
+        <v>24.116823790882982</v>
       </c>
       <c r="D85">
-        <v>55.442087094684233</v>
+        <v>53.449772620070192</v>
       </c>
       <c r="F85" t="s">
-        <v>827</v>
+        <v>843</v>
       </c>
       <c r="G85">
         <v>24.116823790882982</v>
@@ -4898,13 +4946,13 @@
         <v>512</v>
       </c>
       <c r="C86">
-        <v>24.751458444129401</v>
+        <v>24.902804802194161</v>
       </c>
       <c r="D86">
-        <v>55.484738047093231</v>
+        <v>54.931508517983445</v>
       </c>
       <c r="F86" t="s">
-        <v>828</v>
+        <v>844</v>
       </c>
       <c r="G86">
         <v>24.902804802194161</v>
@@ -4918,13 +4966,13 @@
         <v>513</v>
       </c>
       <c r="C87">
-        <v>24.134997638950189</v>
+        <v>25.027949043595768</v>
       </c>
       <c r="D87">
-        <v>55.725534247850831</v>
+        <v>55.165057751776168</v>
       </c>
       <c r="F87" t="s">
-        <v>829</v>
+        <v>845</v>
       </c>
       <c r="G87">
         <v>25.027949043595768</v>
@@ -4938,13 +4986,13 @@
         <v>514</v>
       </c>
       <c r="C88">
-        <v>25.300346276826343</v>
+        <v>24.170593005635538</v>
       </c>
       <c r="D88">
-        <v>55.384268608124387</v>
+        <v>54.42668570728047</v>
       </c>
       <c r="F88" t="s">
-        <v>830</v>
+        <v>846</v>
       </c>
       <c r="G88">
         <v>24.170593005635538</v>
@@ -4958,13 +5006,13 @@
         <v>515</v>
       </c>
       <c r="C89">
-        <v>25.148197475341089</v>
+        <v>23.910974868997364</v>
       </c>
       <c r="D89">
-        <v>55.426029997721258</v>
+        <v>53.702691991144988</v>
       </c>
       <c r="F89" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="G89">
         <v>23.910974868997364</v>
@@ -4978,13 +5026,13 @@
         <v>516</v>
       </c>
       <c r="C90">
-        <v>25.327189474379288</v>
+        <v>24.334856796200501</v>
       </c>
       <c r="D90">
-        <v>55.913131730853088</v>
+        <v>54.588781735586792</v>
       </c>
       <c r="F90" t="s">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="G90">
         <v>24.334856796200501</v>
@@ -4998,13 +5046,13 @@
         <v>517</v>
       </c>
       <c r="C91">
-        <v>25.164284318085173</v>
+        <v>24.537581418017712</v>
       </c>
       <c r="D91">
-        <v>55.375602370041619</v>
+        <v>55.450638077281006</v>
       </c>
       <c r="F91" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="G91">
         <v>24.537581418017712</v>
@@ -5018,13 +5066,13 @@
         <v>518</v>
       </c>
       <c r="C92">
-        <v>25.1414100856991</v>
+        <v>24.529944655230668</v>
       </c>
       <c r="D92">
-        <v>55.471299870306758</v>
+        <v>55.432484246499342</v>
       </c>
       <c r="F92" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="G92">
         <v>24.529944655230668</v>
@@ -5038,13 +5086,13 @@
         <v>519</v>
       </c>
       <c r="C93">
-        <v>25.172994676232289</v>
+        <v>24.129711739367323</v>
       </c>
       <c r="D93">
-        <v>55.294820841065778</v>
+        <v>54.550975842015639</v>
       </c>
       <c r="F93" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="G93">
         <v>24.129711739367323</v>
@@ -5058,13 +5106,13 @@
         <v>520</v>
       </c>
       <c r="C94">
-        <v>25.22175847283016</v>
+        <v>24.769682128938115</v>
       </c>
       <c r="D94">
-        <v>55.40581310000001</v>
+        <v>55.442087094684233</v>
       </c>
       <c r="F94" t="s">
-        <v>836</v>
+        <v>852</v>
       </c>
       <c r="G94">
         <v>24.769682128938115</v>
@@ -5078,13 +5126,13 @@
         <v>521</v>
       </c>
       <c r="C95">
-        <v>24.186800172631759</v>
+        <v>24.751458444129401</v>
       </c>
       <c r="D95">
-        <v>55.321801299835549</v>
+        <v>55.484738047093231</v>
       </c>
       <c r="F95" t="s">
-        <v>837</v>
+        <v>853</v>
       </c>
       <c r="G95">
         <v>24.751458444129401</v>
@@ -5098,13 +5146,13 @@
         <v>522</v>
       </c>
       <c r="C96">
-        <v>23.6505466721282</v>
+        <v>24.134997638950189</v>
       </c>
       <c r="D96">
-        <v>55.565887099999983</v>
+        <v>55.725534247850831</v>
       </c>
       <c r="F96" t="s">
-        <v>838</v>
+        <v>854</v>
       </c>
       <c r="G96">
         <v>24.134997638950189</v>
@@ -5118,13 +5166,13 @@
         <v>523</v>
       </c>
       <c r="C97">
-        <v>23.949551660508689</v>
+        <v>24.116884654343199</v>
       </c>
       <c r="D97">
-        <v>52.229852235410895</v>
+        <v>53.450045589011815</v>
       </c>
       <c r="F97" t="s">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="G97">
         <v>24.116884654343199</v>
@@ -5138,13 +5186,13 @@
         <v>524</v>
       </c>
       <c r="C98">
-        <v>25.014132731296545</v>
+        <v>25.300346276826343</v>
       </c>
       <c r="D98">
-        <v>55.154200895241928</v>
+        <v>55.384268608124387</v>
       </c>
       <c r="F98" t="s">
-        <v>840</v>
+        <v>856</v>
       </c>
       <c r="G98">
         <v>25.300346276826343</v>
@@ -5158,13 +5206,13 @@
         <v>525</v>
       </c>
       <c r="C99">
-        <v>24.12748060097304</v>
+        <v>25.148197475341089</v>
       </c>
       <c r="D99">
-        <v>54.304748689833922</v>
+        <v>55.426029997721258</v>
       </c>
       <c r="F99" t="s">
-        <v>841</v>
+        <v>857</v>
       </c>
       <c r="G99">
         <v>25.148197475341089</v>
@@ -5178,13 +5226,13 @@
         <v>526</v>
       </c>
       <c r="C100">
-        <v>23.770390500134003</v>
+        <v>25.327189474379288</v>
       </c>
       <c r="D100">
-        <v>54.04435810951648</v>
+        <v>55.913131730853088</v>
       </c>
       <c r="F100" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="G100">
         <v>25.327189474379288</v>
@@ -5198,13 +5246,13 @@
         <v>527</v>
       </c>
       <c r="C101">
-        <v>24.035953930227269</v>
+        <v>25.327139055511896</v>
       </c>
       <c r="D101">
-        <v>52.486675927016172</v>
+        <v>55.9128516722661</v>
       </c>
       <c r="F101" t="s">
-        <v>843</v>
+        <v>859</v>
       </c>
       <c r="G101">
         <v>25.327139055511896</v>
@@ -5218,13 +5266,13 @@
         <v>528</v>
       </c>
       <c r="C102">
-        <v>23.038967071929644</v>
+        <v>25.164284318085173</v>
       </c>
       <c r="D102">
-        <v>54.306258699999987</v>
+        <v>55.375602370041619</v>
       </c>
       <c r="F102" t="s">
-        <v>844</v>
+        <v>860</v>
       </c>
       <c r="G102">
         <v>25.164284318085173</v>
@@ -5238,13 +5286,13 @@
         <v>529</v>
       </c>
       <c r="C103">
-        <v>23.770683572172302</v>
+        <v>25.1414100856991</v>
       </c>
       <c r="D103">
-        <v>55.532004600000008</v>
+        <v>55.471299870306758</v>
       </c>
       <c r="F103" t="s">
-        <v>845</v>
+        <v>861</v>
       </c>
       <c r="G103">
         <v>25.1414100856991</v>
@@ -5258,13 +5306,13 @@
         <v>530</v>
       </c>
       <c r="C104">
-        <v>23.775573574933144</v>
+        <v>25.172994676232289</v>
       </c>
       <c r="D104">
-        <v>55.44563626873552</v>
+        <v>55.294820841065778</v>
       </c>
       <c r="F104" t="s">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="G104">
         <v>25.172994676232289</v>
@@ -5278,13 +5326,13 @@
         <v>531</v>
       </c>
       <c r="C105">
-        <v>24.933784559206881</v>
+        <v>25.22175847283016</v>
       </c>
       <c r="D105">
-        <v>55.084212913507841</v>
+        <v>55.40581310000001</v>
       </c>
       <c r="F105" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="G105">
         <v>25.22175847283016</v>
@@ -5298,13 +5346,13 @@
         <v>532</v>
       </c>
       <c r="C106">
-        <v>24.210631553840969</v>
+        <v>24.186800172631759</v>
       </c>
       <c r="D106">
-        <v>54.789737988902679</v>
+        <v>55.321801299835549</v>
       </c>
       <c r="F106" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G106">
         <v>24.186800172631759</v>
@@ -5318,13 +5366,13 @@
         <v>533</v>
       </c>
       <c r="C107">
-        <v>23.007208422155301</v>
+        <v>23.6505466721282</v>
       </c>
       <c r="D107">
-        <v>54.174042150203832</v>
+        <v>55.565887099999983</v>
       </c>
       <c r="F107" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G107">
         <v>23.6505466721282</v>
@@ -5338,13 +5386,13 @@
         <v>534</v>
       </c>
       <c r="C108">
-        <v>24.12182482329224</v>
+        <v>23.949551660508689</v>
       </c>
       <c r="D108">
-        <v>52.603504700926671</v>
+        <v>52.229852235410895</v>
       </c>
       <c r="F108" t="s">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="G108">
         <v>23.949551660508689</v>
@@ -5358,13 +5406,13 @@
         <v>535</v>
       </c>
       <c r="C109">
-        <v>24.269976519758384</v>
+        <v>25.014132731296545</v>
       </c>
       <c r="D109">
-        <v>54.481063735732526</v>
+        <v>55.154200895241928</v>
       </c>
       <c r="F109" t="s">
-        <v>851</v>
+        <v>867</v>
       </c>
       <c r="G109">
         <v>25.014132731296545</v>
@@ -5378,13 +5426,13 @@
         <v>536</v>
       </c>
       <c r="C110">
-        <v>23.572001619424256</v>
+        <v>24.12748060097304</v>
       </c>
       <c r="D110">
-        <v>53.682246684218185</v>
+        <v>54.304748689833922</v>
       </c>
       <c r="F110" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G110">
         <v>24.12748060097304</v>
@@ -5398,13 +5446,13 @@
         <v>537</v>
       </c>
       <c r="C111">
-        <v>24.752127542097561</v>
+        <v>23.770390500134003</v>
       </c>
       <c r="D111">
-        <v>54.704149918718215</v>
+        <v>54.04435810951648</v>
       </c>
       <c r="F111" t="s">
-        <v>853</v>
+        <v>869</v>
       </c>
       <c r="G111">
         <v>23.770390500134003</v>
@@ -5418,13 +5466,13 @@
         <v>538</v>
       </c>
       <c r="C112">
-        <v>25.295347521856549</v>
+        <v>23.949617287945799</v>
       </c>
       <c r="D112">
-        <v>56.34989999176463</v>
+        <v>52.230123131476887</v>
       </c>
       <c r="F112" t="s">
-        <v>854</v>
+        <v>870</v>
       </c>
       <c r="G112">
         <v>23.949617287945799</v>
@@ -5438,13 +5486,13 @@
         <v>539</v>
       </c>
       <c r="C113">
-        <v>24.775066381664931</v>
+        <v>24.035953930227269</v>
       </c>
       <c r="D113">
-        <v>55.348598324087575</v>
+        <v>52.486675927016172</v>
       </c>
       <c r="F113" t="s">
-        <v>855</v>
+        <v>871</v>
       </c>
       <c r="G113">
         <v>24.035953930227269</v>
@@ -5458,13 +5506,13 @@
         <v>540</v>
       </c>
       <c r="C114">
-        <v>23.719606241684648</v>
+        <v>23.038967071929644</v>
       </c>
       <c r="D114">
-        <v>53.495355463951547</v>
+        <v>54.306258699999987</v>
       </c>
       <c r="F114" t="s">
-        <v>856</v>
+        <v>872</v>
       </c>
       <c r="G114">
         <v>23.038967071929644</v>
@@ -5478,13 +5526,13 @@
         <v>541</v>
       </c>
       <c r="C115">
-        <v>24.908855238334628</v>
+        <v>23.770683572172302</v>
       </c>
       <c r="D115">
-        <v>54.916197501856686</v>
+        <v>55.532004600000008</v>
       </c>
       <c r="F115" t="s">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="G115">
         <v>23.770683572172302</v>
@@ -5498,13 +5546,13 @@
         <v>542</v>
       </c>
       <c r="C116">
-        <v>25.020984272725872</v>
+        <v>23.775573574933144</v>
       </c>
       <c r="D116">
-        <v>55.5492943</v>
+        <v>55.44563626873552</v>
       </c>
       <c r="F116" t="s">
-        <v>858</v>
+        <v>874</v>
       </c>
       <c r="G116">
         <v>23.775573574933144</v>
@@ -5518,13 +5566,13 @@
         <v>543</v>
       </c>
       <c r="C117">
-        <v>24.213022472348719</v>
+        <v>24.933784559206881</v>
       </c>
       <c r="D117">
-        <v>55.504416100000007</v>
+        <v>55.084212913507841</v>
       </c>
       <c r="F117" t="s">
-        <v>859</v>
+        <v>875</v>
       </c>
       <c r="G117">
         <v>24.933784559206881</v>
@@ -5538,13 +5586,13 @@
         <v>544</v>
       </c>
       <c r="C118">
-        <v>24.166400422762571</v>
+        <v>24.210631553840969</v>
       </c>
       <c r="D118">
-        <v>54.405774400440784</v>
+        <v>54.789737988902679</v>
       </c>
       <c r="F118" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="G118">
         <v>24.210631553840969</v>
@@ -5558,13 +5606,13 @@
         <v>545</v>
       </c>
       <c r="C119">
-        <v>24.16634508119736</v>
+        <v>23.007208422155301</v>
       </c>
       <c r="D119">
-        <v>54.389197746564257</v>
+        <v>54.174042150203832</v>
       </c>
       <c r="F119" t="s">
-        <v>861</v>
+        <v>877</v>
       </c>
       <c r="G119">
         <v>23.007208422155301</v>
@@ -5578,13 +5626,13 @@
         <v>546</v>
       </c>
       <c r="C120">
-        <v>24.14509232268016</v>
+        <v>24.12182482329224</v>
       </c>
       <c r="D120">
-        <v>54.332525650366243</v>
+        <v>52.603504700926671</v>
       </c>
       <c r="F120" t="s">
-        <v>862</v>
+        <v>878</v>
       </c>
       <c r="G120">
         <v>24.12182482329224</v>
@@ -5598,13 +5646,13 @@
         <v>547</v>
       </c>
       <c r="C121">
-        <v>24.152885722572531</v>
+        <v>24.269976519758384</v>
       </c>
       <c r="D121">
-        <v>54.346075849492713</v>
+        <v>54.481063735732526</v>
       </c>
       <c r="F121" t="s">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="G121">
         <v>24.269976519758384</v>
@@ -5618,13 +5666,13 @@
         <v>548</v>
       </c>
       <c r="C122">
-        <v>24.292737062975348</v>
+        <v>23.572001619424256</v>
       </c>
       <c r="D122">
-        <v>54.506677946264027</v>
+        <v>53.682246684218185</v>
       </c>
       <c r="F122" t="s">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="G122">
         <v>23.572001619424256</v>
@@ -5638,13 +5686,13 @@
         <v>549</v>
       </c>
       <c r="C123">
-        <v>24.150433472322405</v>
+        <v>24.752127542097561</v>
       </c>
       <c r="D123">
-        <v>52.58740259999999</v>
+        <v>54.704149918718215</v>
       </c>
       <c r="F123" t="s">
-        <v>865</v>
+        <v>881</v>
       </c>
       <c r="G123">
         <v>24.752127542097561</v>
@@ -5658,13 +5706,13 @@
         <v>550</v>
       </c>
       <c r="C124">
-        <v>25.324933788832251</v>
+        <v>25.295347521856549</v>
       </c>
       <c r="D124">
-        <v>55.604564220737281</v>
+        <v>56.34989999176463</v>
       </c>
       <c r="F124" t="s">
-        <v>866</v>
+        <v>882</v>
       </c>
       <c r="G124">
         <v>25.295347521856549</v>
@@ -5678,13 +5726,13 @@
         <v>551</v>
       </c>
       <c r="C125">
-        <v>24.650469972544329</v>
+        <v>24.775066381664931</v>
       </c>
       <c r="D125">
-        <v>54.755590200000015</v>
+        <v>55.348598324087575</v>
       </c>
       <c r="F125" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="G125">
         <v>24.775066381664931</v>
@@ -5698,13 +5746,13 @@
         <v>552</v>
       </c>
       <c r="C126">
-        <v>24.31633147239307</v>
+        <v>23.719606241684648</v>
       </c>
       <c r="D126">
-        <v>54.793931799999989</v>
+        <v>53.495355463951547</v>
       </c>
       <c r="F126" t="s">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="G126">
         <v>23.719606241684648</v>
@@ -5718,13 +5766,13 @@
         <v>553</v>
       </c>
       <c r="C127">
-        <v>23.903319772332694</v>
+        <v>24.908855238334628</v>
       </c>
       <c r="D127">
-        <v>55.497729900106187</v>
+        <v>54.916197501856686</v>
       </c>
       <c r="F127" t="s">
-        <v>869</v>
+        <v>885</v>
       </c>
       <c r="G127">
         <v>24.908855238334628</v>
@@ -5738,13 +5786,13 @@
         <v>554</v>
       </c>
       <c r="C128">
-        <v>24.026718572271779</v>
+        <v>25.020984272725872</v>
       </c>
       <c r="D128">
-        <v>52.770564500000006</v>
+        <v>55.5492943</v>
       </c>
       <c r="F128" t="s">
-        <v>870</v>
+        <v>886</v>
       </c>
       <c r="G128">
         <v>25.020984272725872</v>
@@ -5758,13 +5806,13 @@
         <v>555</v>
       </c>
       <c r="C129">
-        <v>24.247282672363291</v>
+        <v>24.213022472348719</v>
       </c>
       <c r="D129">
-        <v>56.120600600000003</v>
+        <v>55.504416100000007</v>
       </c>
       <c r="F129" t="s">
-        <v>871</v>
+        <v>887</v>
       </c>
       <c r="G129">
         <v>24.213022472348719</v>
@@ -5778,13 +5826,13 @@
         <v>556</v>
       </c>
       <c r="C130">
-        <v>24.531414972489035</v>
+        <v>24.166400422762571</v>
       </c>
       <c r="D130">
-        <v>50.880768199999991</v>
+        <v>54.405774400440784</v>
       </c>
       <c r="F130" t="s">
-        <v>872</v>
+        <v>888</v>
       </c>
       <c r="G130">
         <v>24.166400422762571</v>
@@ -5798,13 +5846,13 @@
         <v>557</v>
       </c>
       <c r="C131">
-        <v>24.988041872709147</v>
+        <v>24.16634508119736</v>
       </c>
       <c r="D131">
-        <v>55.539364800000001</v>
+        <v>54.389197746564257</v>
       </c>
       <c r="F131" t="s">
-        <v>873</v>
+        <v>889</v>
       </c>
       <c r="G131">
         <v>24.16634508119736</v>
@@ -5818,13 +5866,13 @@
         <v>558</v>
       </c>
       <c r="C132">
-        <v>23.628846114498661</v>
+        <v>24.14509232268016</v>
       </c>
       <c r="D132">
-        <v>51.975078053017697</v>
+        <v>54.332525650366243</v>
       </c>
       <c r="F132" t="s">
-        <v>874</v>
+        <v>890</v>
       </c>
       <c r="G132">
         <v>24.14509232268016</v>
@@ -5838,13 +5886,13 @@
         <v>559</v>
       </c>
       <c r="C133">
-        <v>24.401828191757645</v>
+        <v>24.152885722572531</v>
       </c>
       <c r="D133">
-        <v>51.766710350850722</v>
+        <v>54.346075849492713</v>
       </c>
       <c r="F133" t="s">
-        <v>875</v>
+        <v>891</v>
       </c>
       <c r="G133">
         <v>24.152885722572531</v>
@@ -5858,13 +5906,13 @@
         <v>560</v>
       </c>
       <c r="C134">
-        <v>23.926851843606507</v>
+        <v>24.127538178805121</v>
       </c>
       <c r="D134">
-        <v>53.529128664302512</v>
+        <v>54.30502273919538</v>
       </c>
       <c r="F134" t="s">
-        <v>876</v>
+        <v>892</v>
       </c>
       <c r="G134">
         <v>24.127538178805121</v>
@@ -5878,13 +5926,13 @@
         <v>561</v>
       </c>
       <c r="C135">
-        <v>23.288891966596964</v>
+        <v>24.270033308710161</v>
       </c>
       <c r="D135">
-        <v>52.856887386147065</v>
+        <v>54.481338475257807</v>
       </c>
       <c r="F135" t="s">
-        <v>877</v>
+        <v>893</v>
       </c>
       <c r="G135">
         <v>24.270033308710161</v>
@@ -5898,13 +5946,13 @@
         <v>562</v>
       </c>
       <c r="C136">
-        <v>23.216188760856237</v>
+        <v>24.292737062975348</v>
       </c>
       <c r="D136">
-        <v>53.78974274720256</v>
+        <v>54.506677946264027</v>
       </c>
       <c r="F136" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="G136">
         <v>24.292737062975348</v>
@@ -5918,13 +5966,13 @@
         <v>563</v>
       </c>
       <c r="C137">
-        <v>24.80726575531164</v>
+        <v>24.150433472322405</v>
       </c>
       <c r="D137">
-        <v>55.083131109854811</v>
+        <v>52.58740259999999</v>
       </c>
       <c r="F137" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="G137">
         <v>24.150433472322405</v>
@@ -5938,13 +5986,13 @@
         <v>564</v>
       </c>
       <c r="C138">
-        <v>25.07685924672872</v>
+        <v>25.324933788832251</v>
       </c>
       <c r="D138">
-        <v>55.759366661200495</v>
+        <v>55.604564220737281</v>
       </c>
       <c r="F138" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="G138">
         <v>25.324933788832251</v>
@@ -5958,13 +6006,13 @@
         <v>565</v>
       </c>
       <c r="C139">
-        <v>24.356500000000004</v>
+        <v>25.370222011372469</v>
       </c>
       <c r="D139">
-        <v>55.644837518894228</v>
+        <v>55.46616511750441</v>
       </c>
       <c r="F139" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="G139">
         <v>25.370222011372469</v>
@@ -5978,13 +6026,13 @@
         <v>566</v>
       </c>
       <c r="C140">
-        <v>24.128498236636499</v>
+        <v>24.650469972544329</v>
       </c>
       <c r="D140">
-        <v>54.895489405640042</v>
+        <v>54.755590200000015</v>
       </c>
       <c r="F140" t="s">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="G140">
         <v>24.650469972544329</v>
@@ -5998,13 +6046,13 @@
         <v>567</v>
       </c>
       <c r="C141">
-        <v>23.233928858937865</v>
+        <v>24.31633147239307</v>
       </c>
       <c r="D141">
-        <v>54.914457464905659</v>
+        <v>54.793931799999989</v>
       </c>
       <c r="F141" t="s">
-        <v>883</v>
+        <v>899</v>
       </c>
       <c r="G141">
         <v>24.31633147239307</v>
@@ -6018,13 +6066,13 @@
         <v>568</v>
       </c>
       <c r="C142">
-        <v>23.354936307932626</v>
+        <v>24.2926803892084</v>
       </c>
       <c r="D142">
-        <v>52.336071807165887</v>
+        <v>54.506403099946027</v>
       </c>
       <c r="F142" t="s">
-        <v>884</v>
+        <v>900</v>
       </c>
       <c r="G142">
         <v>24.2926803892084</v>
@@ -6038,13 +6086,13 @@
         <v>569</v>
       </c>
       <c r="C143">
-        <v>23.920654293789596</v>
+        <v>23.903319772332694</v>
       </c>
       <c r="D143">
-        <v>52.200515747711748</v>
+        <v>55.497729900106187</v>
       </c>
       <c r="F143" t="s">
-        <v>885</v>
+        <v>901</v>
       </c>
       <c r="G143">
         <v>23.903319772332694</v>
@@ -6058,13 +6106,13 @@
         <v>570</v>
       </c>
       <c r="C144">
-        <v>23.218211227778148</v>
+        <v>24.026718572271779</v>
       </c>
       <c r="D144">
-        <v>53.926237102402403</v>
+        <v>52.770564500000006</v>
       </c>
       <c r="F144" t="s">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="G144">
         <v>24.026718572271779</v>
@@ -6078,13 +6126,13 @@
         <v>571</v>
       </c>
       <c r="C145">
-        <v>23.931227967096429</v>
+        <v>24.247282672363291</v>
       </c>
       <c r="D145">
-        <v>53.469560174878147</v>
+        <v>56.120600600000003</v>
       </c>
       <c r="F145" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="G145">
         <v>24.247282672363291</v>
@@ -6098,13 +6146,13 @@
         <v>572</v>
       </c>
       <c r="C146">
-        <v>23.979160726435538</v>
+        <v>24.531414972489035</v>
       </c>
       <c r="D146">
-        <v>54.475940169716061</v>
+        <v>50.880768199999991</v>
       </c>
       <c r="F146" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="G146">
         <v>24.531414972489035</v>
@@ -6118,13 +6166,13 @@
         <v>573</v>
       </c>
       <c r="C147">
-        <v>24.999105828807476</v>
+        <v>24.988041872709147</v>
       </c>
       <c r="D147">
-        <v>56.132076810006872</v>
+        <v>55.539364800000001</v>
       </c>
       <c r="F147" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="G147">
         <v>24.988041872709147</v>
@@ -6138,13 +6186,13 @@
         <v>574</v>
       </c>
       <c r="C148">
-        <v>24.869387007749022</v>
+        <v>23.628846114498661</v>
       </c>
       <c r="D148">
-        <v>55.465573088530363</v>
+        <v>51.975078053017697</v>
       </c>
       <c r="F148" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="G148">
         <v>23.628846114498661</v>
@@ -6158,13 +6206,13 @@
         <v>575</v>
       </c>
       <c r="C149">
-        <v>24.093596672005251</v>
+        <v>24.401828191757645</v>
       </c>
       <c r="D149">
-        <v>56.132076810006872</v>
+        <v>51.766710350850722</v>
       </c>
       <c r="F149" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="G149">
         <v>24.401828191757645</v>
@@ -6178,13 +6226,13 @@
         <v>576</v>
       </c>
       <c r="C150">
-        <v>23.301781193339448</v>
+        <v>23.926851843606507</v>
       </c>
       <c r="D150">
-        <v>55.310998429692894</v>
+        <v>53.529128664302512</v>
       </c>
       <c r="F150" t="s">
-        <v>892</v>
+        <v>908</v>
       </c>
       <c r="G150">
         <v>23.926851843606507</v>
@@ -6198,13 +6246,13 @@
         <v>577</v>
       </c>
       <c r="C151">
-        <v>24.095660810855893</v>
+        <v>23.288891966596964</v>
       </c>
       <c r="D151">
-        <v>55.354583988181886</v>
+        <v>52.856887386147065</v>
       </c>
       <c r="F151" t="s">
-        <v>893</v>
+        <v>909</v>
       </c>
       <c r="G151">
         <v>23.288891966596964</v>
@@ -6218,13 +6266,13 @@
         <v>578</v>
       </c>
       <c r="C152">
-        <v>25.652609726915191</v>
+        <v>23.216188760856237</v>
       </c>
       <c r="D152">
-        <v>52.850882041633369</v>
+        <v>53.78974274720256</v>
       </c>
       <c r="F152" t="s">
-        <v>894</v>
+        <v>910</v>
       </c>
       <c r="G152">
         <v>23.216188760856237</v>
@@ -6238,13 +6286,13 @@
         <v>579</v>
       </c>
       <c r="C153">
-        <v>25.652609726915191</v>
+        <v>24.80726575531164</v>
       </c>
       <c r="D153">
-        <v>53.338128534372927</v>
+        <v>55.083131109854811</v>
       </c>
       <c r="F153" t="s">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="G153">
         <v>24.80726575531164</v>
@@ -6254,8 +6302,17 @@
       </c>
     </row>
     <row r="154" spans="2:8">
+      <c r="B154" t="s">
+        <v>580</v>
+      </c>
+      <c r="C154">
+        <v>25.07685924672872</v>
+      </c>
+      <c r="D154">
+        <v>55.759366661200495</v>
+      </c>
       <c r="F154" t="s">
-        <v>896</v>
+        <v>912</v>
       </c>
       <c r="G154">
         <v>25.07685924672872</v>
@@ -6265,8 +6322,17 @@
       </c>
     </row>
     <row r="155" spans="2:8">
+      <c r="B155" t="s">
+        <v>581</v>
+      </c>
+      <c r="C155">
+        <v>24.356500000000004</v>
+      </c>
+      <c r="D155">
+        <v>55.644837518894228</v>
+      </c>
       <c r="F155" t="s">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="G155">
         <v>24.356500000000004</v>
@@ -6276,8 +6342,17 @@
       </c>
     </row>
     <row r="156" spans="2:8">
+      <c r="B156" t="s">
+        <v>582</v>
+      </c>
+      <c r="C156">
+        <v>24.128498236636499</v>
+      </c>
+      <c r="D156">
+        <v>54.895489405640042</v>
+      </c>
       <c r="F156" t="s">
-        <v>898</v>
+        <v>914</v>
       </c>
       <c r="G156">
         <v>24.128498236636499</v>
@@ -6287,8 +6362,17 @@
       </c>
     </row>
     <row r="157" spans="2:8">
+      <c r="B157" t="s">
+        <v>583</v>
+      </c>
+      <c r="C157">
+        <v>23.233928858937865</v>
+      </c>
+      <c r="D157">
+        <v>54.914457464905659</v>
+      </c>
       <c r="F157" t="s">
-        <v>899</v>
+        <v>915</v>
       </c>
       <c r="G157">
         <v>23.233928858937865</v>
@@ -6298,8 +6382,17 @@
       </c>
     </row>
     <row r="158" spans="2:8">
+      <c r="B158" t="s">
+        <v>584</v>
+      </c>
+      <c r="C158">
+        <v>23.354936307932626</v>
+      </c>
+      <c r="D158">
+        <v>52.336071807165887</v>
+      </c>
       <c r="F158" t="s">
-        <v>900</v>
+        <v>916</v>
       </c>
       <c r="G158">
         <v>23.354936307932626</v>
@@ -6309,8 +6402,17 @@
       </c>
     </row>
     <row r="159" spans="2:8">
+      <c r="B159" t="s">
+        <v>585</v>
+      </c>
+      <c r="C159">
+        <v>23.920654293789596</v>
+      </c>
+      <c r="D159">
+        <v>52.200515747711748</v>
+      </c>
       <c r="F159" t="s">
-        <v>901</v>
+        <v>917</v>
       </c>
       <c r="G159">
         <v>23.920654293789596</v>
@@ -6320,8 +6422,17 @@
       </c>
     </row>
     <row r="160" spans="2:8">
+      <c r="B160" t="s">
+        <v>586</v>
+      </c>
+      <c r="C160">
+        <v>23.218211227778148</v>
+      </c>
+      <c r="D160">
+        <v>53.926237102402403</v>
+      </c>
       <c r="F160" t="s">
-        <v>902</v>
+        <v>918</v>
       </c>
       <c r="G160">
         <v>23.218211227778148</v>
@@ -6330,9 +6441,18 @@
         <v>53.926237102402403</v>
       </c>
     </row>
-    <row r="161" spans="6:8">
+    <row r="161" spans="2:8">
+      <c r="B161" t="s">
+        <v>587</v>
+      </c>
+      <c r="C161">
+        <v>23.931227967096429</v>
+      </c>
+      <c r="D161">
+        <v>53.469560174878147</v>
+      </c>
       <c r="F161" t="s">
-        <v>903</v>
+        <v>919</v>
       </c>
       <c r="G161">
         <v>23.931227967096429</v>
@@ -6341,9 +6461,18 @@
         <v>53.469560174878147</v>
       </c>
     </row>
-    <row r="162" spans="6:8">
+    <row r="162" spans="2:8">
+      <c r="B162" t="s">
+        <v>588</v>
+      </c>
+      <c r="C162">
+        <v>23.979160726435538</v>
+      </c>
+      <c r="D162">
+        <v>54.475940169716061</v>
+      </c>
       <c r="F162" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
       <c r="G162">
         <v>23.979160726435538</v>
@@ -6352,9 +6481,18 @@
         <v>54.475940169716061</v>
       </c>
     </row>
-    <row r="163" spans="6:8">
+    <row r="163" spans="2:8">
+      <c r="B163" t="s">
+        <v>589</v>
+      </c>
+      <c r="C163">
+        <v>24.999105828807476</v>
+      </c>
+      <c r="D163">
+        <v>56.132076810006872</v>
+      </c>
       <c r="F163" t="s">
-        <v>905</v>
+        <v>921</v>
       </c>
       <c r="G163">
         <v>24.999105828807476</v>
@@ -6363,9 +6501,18 @@
         <v>56.132076810006872</v>
       </c>
     </row>
-    <row r="164" spans="6:8">
+    <row r="164" spans="2:8">
+      <c r="B164" t="s">
+        <v>590</v>
+      </c>
+      <c r="C164">
+        <v>24.869387007749022</v>
+      </c>
+      <c r="D164">
+        <v>55.465573088530363</v>
+      </c>
       <c r="F164" t="s">
-        <v>906</v>
+        <v>922</v>
       </c>
       <c r="G164">
         <v>24.869387007749022</v>
@@ -6374,9 +6521,18 @@
         <v>55.465573088530363</v>
       </c>
     </row>
-    <row r="165" spans="6:8">
+    <row r="165" spans="2:8">
+      <c r="B165" t="s">
+        <v>591</v>
+      </c>
+      <c r="C165">
+        <v>24.093596672005251</v>
+      </c>
+      <c r="D165">
+        <v>56.132076810006872</v>
+      </c>
       <c r="F165" t="s">
-        <v>907</v>
+        <v>923</v>
       </c>
       <c r="G165">
         <v>24.093596672005251</v>
@@ -6385,9 +6541,18 @@
         <v>56.132076810006872</v>
       </c>
     </row>
-    <row r="166" spans="6:8">
+    <row r="166" spans="2:8">
+      <c r="B166" t="s">
+        <v>592</v>
+      </c>
+      <c r="C166">
+        <v>23.301781193339448</v>
+      </c>
+      <c r="D166">
+        <v>55.310998429692894</v>
+      </c>
       <c r="F166" t="s">
-        <v>908</v>
+        <v>924</v>
       </c>
       <c r="G166">
         <v>23.301781193339448</v>
@@ -6396,9 +6561,18 @@
         <v>55.310998429692894</v>
       </c>
     </row>
-    <row r="167" spans="6:8">
+    <row r="167" spans="2:8">
+      <c r="B167" t="s">
+        <v>593</v>
+      </c>
+      <c r="C167">
+        <v>24.095660810855893</v>
+      </c>
+      <c r="D167">
+        <v>55.354583988181886</v>
+      </c>
       <c r="F167" t="s">
-        <v>909</v>
+        <v>925</v>
       </c>
       <c r="G167">
         <v>24.095660810855893</v>
@@ -6407,9 +6581,18 @@
         <v>55.354583988181886</v>
       </c>
     </row>
-    <row r="168" spans="6:8">
+    <row r="168" spans="2:8">
+      <c r="B168" t="s">
+        <v>594</v>
+      </c>
+      <c r="C168">
+        <v>25.652609726915191</v>
+      </c>
+      <c r="D168">
+        <v>52.850882041633369</v>
+      </c>
       <c r="F168" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="G168">
         <v>25.652609726915191</v>
@@ -6418,9 +6601,18 @@
         <v>52.850882041633369</v>
       </c>
     </row>
-    <row r="169" spans="6:8">
+    <row r="169" spans="2:8">
+      <c r="B169" t="s">
+        <v>595</v>
+      </c>
+      <c r="C169">
+        <v>25.652609726915191</v>
+      </c>
+      <c r="D169">
+        <v>53.338128534372927</v>
+      </c>
       <c r="F169" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="G169">
         <v>25.652609726915191</v>
@@ -19606,7 +19798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AB0CAE-315A-4F19-935E-D4E6A80B7911}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6122EEEE-5A41-4998-8599-47D862430E5B}">
   <dimension ref="B9:L169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19664,19 +19856,19 @@
         <v>437</v>
       </c>
       <c r="G11" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H11" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J11" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K11" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="L11" t="s">
-        <v>591</v>
+        <v>607</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -19693,19 +19885,19 @@
         <v>438</v>
       </c>
       <c r="G12" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H12" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J12" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K12" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="L12" t="s">
-        <v>592</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -19722,19 +19914,19 @@
         <v>439</v>
       </c>
       <c r="G13" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H13" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="J13" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K13" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="L13" t="s">
-        <v>593</v>
+        <v>609</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -19751,19 +19943,19 @@
         <v>440</v>
       </c>
       <c r="G14" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H14" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="J14" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K14" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="L14" t="s">
-        <v>594</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -19780,19 +19972,19 @@
         <v>441</v>
       </c>
       <c r="G15" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H15" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="J15" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K15" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="L15" t="s">
-        <v>595</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -19809,19 +20001,19 @@
         <v>442</v>
       </c>
       <c r="G16" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H16" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="J16" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K16" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="L16" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -19838,19 +20030,19 @@
         <v>443</v>
       </c>
       <c r="G17" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H17" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J17" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K17" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="L17" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -19867,19 +20059,19 @@
         <v>444</v>
       </c>
       <c r="G18" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H18" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J18" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K18" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="L18" t="s">
-        <v>598</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -19896,19 +20088,19 @@
         <v>445</v>
       </c>
       <c r="G19" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H19" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="J19" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K19" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="L19" t="s">
-        <v>599</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -19925,19 +20117,19 @@
         <v>446</v>
       </c>
       <c r="G20" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H20" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="J20" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K20" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="L20" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -19954,19 +20146,19 @@
         <v>447</v>
       </c>
       <c r="G21" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H21" t="s">
-        <v>581</v>
+        <v>600</v>
       </c>
       <c r="J21" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K21" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="L21" t="s">
-        <v>601</v>
+        <v>617</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -19983,19 +20175,19 @@
         <v>448</v>
       </c>
       <c r="G22" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H22" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="J22" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K22" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="L22" t="s">
-        <v>602</v>
+        <v>618</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -20012,19 +20204,19 @@
         <v>449</v>
       </c>
       <c r="G23" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H23" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J23" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K23" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="L23" t="s">
-        <v>603</v>
+        <v>619</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -20041,19 +20233,19 @@
         <v>450</v>
       </c>
       <c r="G24" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H24" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J24" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K24" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="L24" t="s">
-        <v>604</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -20070,19 +20262,19 @@
         <v>451</v>
       </c>
       <c r="G25" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H25" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J25" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K25" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="L25" t="s">
-        <v>605</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -20099,19 +20291,19 @@
         <v>452</v>
       </c>
       <c r="G26" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H26" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J26" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K26" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="L26" t="s">
-        <v>606</v>
+        <v>622</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -20128,19 +20320,19 @@
         <v>453</v>
       </c>
       <c r="G27" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H27" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J27" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K27" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="L27" t="s">
-        <v>607</v>
+        <v>623</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -20157,19 +20349,19 @@
         <v>454</v>
       </c>
       <c r="G28" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H28" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J28" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K28" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="L28" t="s">
-        <v>608</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -20186,19 +20378,19 @@
         <v>455</v>
       </c>
       <c r="G29" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H29" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J29" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K29" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
       <c r="L29" t="s">
-        <v>609</v>
+        <v>625</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -20215,19 +20407,19 @@
         <v>456</v>
       </c>
       <c r="G30" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H30" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J30" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K30" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
       <c r="L30" t="s">
-        <v>610</v>
+        <v>626</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -20244,19 +20436,19 @@
         <v>457</v>
       </c>
       <c r="G31" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H31" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J31" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K31" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="L31" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -20273,19 +20465,19 @@
         <v>458</v>
       </c>
       <c r="G32" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H32" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J32" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K32" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="L32" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -20302,19 +20494,19 @@
         <v>459</v>
       </c>
       <c r="G33" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H33" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J33" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K33" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="L33" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -20331,19 +20523,19 @@
         <v>460</v>
       </c>
       <c r="G34" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H34" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="J34" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K34" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
       <c r="L34" t="s">
-        <v>614</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -20360,19 +20552,19 @@
         <v>461</v>
       </c>
       <c r="G35" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H35" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J35" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K35" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
       <c r="L35" t="s">
-        <v>615</v>
+        <v>631</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -20389,19 +20581,19 @@
         <v>462</v>
       </c>
       <c r="G36" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H36" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J36" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K36" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
       <c r="L36" t="s">
-        <v>616</v>
+        <v>632</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -20418,19 +20610,19 @@
         <v>463</v>
       </c>
       <c r="G37" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H37" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="J37" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K37" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
       <c r="L37" t="s">
-        <v>617</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -20447,19 +20639,19 @@
         <v>464</v>
       </c>
       <c r="G38" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H38" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="J38" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K38" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="L38" t="s">
-        <v>618</v>
+        <v>634</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -20476,19 +20668,19 @@
         <v>465</v>
       </c>
       <c r="G39" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H39" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J39" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K39" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="L39" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -20505,19 +20697,19 @@
         <v>466</v>
       </c>
       <c r="G40" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H40" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J40" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K40" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="L40" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -20534,19 +20726,19 @@
         <v>467</v>
       </c>
       <c r="G41" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H41" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J41" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K41" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="L41" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -20563,19 +20755,19 @@
         <v>468</v>
       </c>
       <c r="G42" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H42" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
       <c r="J42" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K42" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
       <c r="L42" t="s">
-        <v>622</v>
+        <v>638</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -20592,19 +20784,19 @@
         <v>469</v>
       </c>
       <c r="G43" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H43" t="s">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="J43" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K43" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="L43" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -20621,19 +20813,19 @@
         <v>470</v>
       </c>
       <c r="G44" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H44" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="J44" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K44" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="L44" t="s">
-        <v>624</v>
+        <v>640</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -20650,19 +20842,19 @@
         <v>471</v>
       </c>
       <c r="G45" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H45" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J45" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K45" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
       <c r="L45" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -20679,19 +20871,19 @@
         <v>472</v>
       </c>
       <c r="G46" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H46" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J46" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K46" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="L46" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -20708,19 +20900,19 @@
         <v>473</v>
       </c>
       <c r="G47" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H47" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J47" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K47" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="L47" t="s">
-        <v>627</v>
+        <v>643</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -20737,19 +20929,19 @@
         <v>474</v>
       </c>
       <c r="G48" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H48" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J48" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K48" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="L48" t="s">
-        <v>628</v>
+        <v>644</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -20766,19 +20958,19 @@
         <v>475</v>
       </c>
       <c r="G49" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H49" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="J49" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K49" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="L49" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -20795,19 +20987,19 @@
         <v>476</v>
       </c>
       <c r="G50" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H50" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J50" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K50" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="L50" t="s">
-        <v>630</v>
+        <v>646</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -20824,19 +21016,19 @@
         <v>477</v>
       </c>
       <c r="G51" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H51" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J51" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K51" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="L51" t="s">
-        <v>631</v>
+        <v>647</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -20853,19 +21045,19 @@
         <v>478</v>
       </c>
       <c r="G52" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H52" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J52" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K52" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="L52" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -20882,19 +21074,19 @@
         <v>479</v>
       </c>
       <c r="G53" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H53" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J53" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K53" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
       <c r="L53" t="s">
-        <v>633</v>
+        <v>649</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -20911,19 +21103,19 @@
         <v>480</v>
       </c>
       <c r="G54" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H54" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J54" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K54" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
       <c r="L54" t="s">
-        <v>634</v>
+        <v>650</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -20940,19 +21132,19 @@
         <v>481</v>
       </c>
       <c r="G55" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H55" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J55" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K55" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="L55" t="s">
-        <v>635</v>
+        <v>651</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -20969,19 +21161,19 @@
         <v>482</v>
       </c>
       <c r="G56" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H56" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="J56" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K56" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="L56" t="s">
-        <v>636</v>
+        <v>652</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -20998,19 +21190,19 @@
         <v>483</v>
       </c>
       <c r="G57" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H57" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J57" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K57" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="L57" t="s">
-        <v>637</v>
+        <v>653</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -21027,19 +21219,19 @@
         <v>484</v>
       </c>
       <c r="G58" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H58" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J58" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K58" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="L58" t="s">
-        <v>638</v>
+        <v>654</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -21056,19 +21248,19 @@
         <v>485</v>
       </c>
       <c r="G59" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H59" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J59" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K59" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="L59" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -21085,19 +21277,19 @@
         <v>486</v>
       </c>
       <c r="G60" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H60" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J60" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K60" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="L60" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -21114,19 +21306,19 @@
         <v>487</v>
       </c>
       <c r="G61" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H61" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J61" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K61" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
       <c r="L61" t="s">
-        <v>641</v>
+        <v>657</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -21143,19 +21335,19 @@
         <v>488</v>
       </c>
       <c r="G62" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H62" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="J62" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K62" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
       <c r="L62" t="s">
-        <v>642</v>
+        <v>658</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -21172,19 +21364,19 @@
         <v>489</v>
       </c>
       <c r="G63" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H63" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J63" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K63" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="L63" t="s">
-        <v>643</v>
+        <v>659</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -21201,19 +21393,19 @@
         <v>490</v>
       </c>
       <c r="G64" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H64" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="J64" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K64" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
       <c r="L64" t="s">
-        <v>644</v>
+        <v>660</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -21230,19 +21422,19 @@
         <v>491</v>
       </c>
       <c r="G65" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H65" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J65" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K65" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="L65" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -21259,19 +21451,19 @@
         <v>492</v>
       </c>
       <c r="G66" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H66" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="J66" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K66" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
       <c r="L66" t="s">
-        <v>646</v>
+        <v>662</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -21288,19 +21480,19 @@
         <v>493</v>
       </c>
       <c r="G67" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H67" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J67" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K67" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="L67" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -21317,19 +21509,19 @@
         <v>494</v>
       </c>
       <c r="G68" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H68" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J68" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K68" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="L68" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -21346,19 +21538,19 @@
         <v>495</v>
       </c>
       <c r="G69" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H69" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J69" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K69" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="L69" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -21375,19 +21567,19 @@
         <v>496</v>
       </c>
       <c r="G70" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H70" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="J70" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K70" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="L70" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -21404,19 +21596,19 @@
         <v>497</v>
       </c>
       <c r="G71" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H71" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J71" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K71" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="L71" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -21433,19 +21625,19 @@
         <v>498</v>
       </c>
       <c r="G72" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H72" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J72" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K72" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="L72" t="s">
-        <v>652</v>
+        <v>668</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -21462,19 +21654,19 @@
         <v>499</v>
       </c>
       <c r="G73" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H73" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J73" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K73" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
       <c r="L73" t="s">
-        <v>653</v>
+        <v>669</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -21491,19 +21683,19 @@
         <v>500</v>
       </c>
       <c r="G74" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H74" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J74" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K74" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="L74" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -21520,19 +21712,19 @@
         <v>501</v>
       </c>
       <c r="G75" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H75" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="J75" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K75" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="L75" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -21549,19 +21741,19 @@
         <v>502</v>
       </c>
       <c r="G76" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H76" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J76" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K76" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
       <c r="L76" t="s">
-        <v>656</v>
+        <v>672</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -21578,19 +21770,19 @@
         <v>503</v>
       </c>
       <c r="G77" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H77" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J77" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K77" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
       <c r="L77" t="s">
-        <v>657</v>
+        <v>673</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -21607,19 +21799,19 @@
         <v>504</v>
       </c>
       <c r="G78" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H78" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="J78" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K78" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
       <c r="L78" t="s">
-        <v>658</v>
+        <v>674</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -21636,19 +21828,19 @@
         <v>505</v>
       </c>
       <c r="G79" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H79" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J79" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K79" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="L79" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -21665,19 +21857,19 @@
         <v>506</v>
       </c>
       <c r="G80" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H80" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J80" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K80" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
       <c r="L80" t="s">
-        <v>660</v>
+        <v>676</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -21694,19 +21886,19 @@
         <v>507</v>
       </c>
       <c r="G81" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H81" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J81" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K81" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="L81" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -21723,19 +21915,19 @@
         <v>508</v>
       </c>
       <c r="G82" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H82" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J82" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K82" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="L82" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -21752,19 +21944,19 @@
         <v>509</v>
       </c>
       <c r="G83" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H83" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J83" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K83" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="L83" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -21781,19 +21973,19 @@
         <v>510</v>
       </c>
       <c r="G84" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H84" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J84" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K84" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="L84" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -21810,19 +22002,19 @@
         <v>511</v>
       </c>
       <c r="G85" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H85" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J85" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K85" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
       <c r="L85" t="s">
-        <v>665</v>
+        <v>681</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -21839,19 +22031,19 @@
         <v>512</v>
       </c>
       <c r="G86" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H86" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J86" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K86" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="L86" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -21868,19 +22060,19 @@
         <v>513</v>
       </c>
       <c r="G87" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H87" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J87" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K87" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
       <c r="L87" t="s">
-        <v>667</v>
+        <v>683</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -21897,19 +22089,19 @@
         <v>514</v>
       </c>
       <c r="G88" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H88" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="J88" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K88" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
       <c r="L88" t="s">
-        <v>668</v>
+        <v>684</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -21926,19 +22118,19 @@
         <v>515</v>
       </c>
       <c r="G89" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H89" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J89" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K89" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
       <c r="L89" t="s">
-        <v>669</v>
+        <v>685</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -21955,19 +22147,19 @@
         <v>516</v>
       </c>
       <c r="G90" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H90" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="J90" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K90" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="L90" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -21984,19 +22176,19 @@
         <v>517</v>
       </c>
       <c r="G91" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H91" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J91" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K91" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="L91" t="s">
-        <v>671</v>
+        <v>687</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -22013,19 +22205,19 @@
         <v>518</v>
       </c>
       <c r="G92" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H92" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J92" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K92" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
       <c r="L92" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -22042,19 +22234,19 @@
         <v>519</v>
       </c>
       <c r="G93" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H93" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J93" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K93" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="L93" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -22071,19 +22263,19 @@
         <v>520</v>
       </c>
       <c r="G94" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H94" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="J94" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K94" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
       <c r="L94" t="s">
-        <v>674</v>
+        <v>690</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -22100,19 +22292,19 @@
         <v>521</v>
       </c>
       <c r="G95" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H95" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J95" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K95" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
       <c r="L95" t="s">
-        <v>675</v>
+        <v>691</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -22129,19 +22321,19 @@
         <v>522</v>
       </c>
       <c r="G96" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H96" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="J96" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K96" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
       <c r="L96" t="s">
-        <v>676</v>
+        <v>692</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -22158,19 +22350,19 @@
         <v>523</v>
       </c>
       <c r="G97" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H97" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J97" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K97" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="L97" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -22187,19 +22379,19 @@
         <v>524</v>
       </c>
       <c r="G98" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H98" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="J98" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K98" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="L98" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -22216,19 +22408,19 @@
         <v>525</v>
       </c>
       <c r="G99" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H99" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J99" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K99" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="L99" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -22245,19 +22437,19 @@
         <v>526</v>
       </c>
       <c r="G100" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H100" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="J100" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K100" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="L100" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -22274,19 +22466,19 @@
         <v>527</v>
       </c>
       <c r="G101" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H101" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="J101" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K101" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="L101" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -22303,19 +22495,19 @@
         <v>528</v>
       </c>
       <c r="G102" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H102" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J102" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K102" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="L102" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -22332,19 +22524,19 @@
         <v>529</v>
       </c>
       <c r="G103" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H103" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J103" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K103" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
       <c r="L103" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -22361,19 +22553,19 @@
         <v>530</v>
       </c>
       <c r="G104" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H104" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J104" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K104" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="L104" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -22390,19 +22582,19 @@
         <v>531</v>
       </c>
       <c r="G105" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H105" t="s">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="J105" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K105" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
       <c r="L105" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -22419,19 +22611,19 @@
         <v>532</v>
       </c>
       <c r="G106" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H106" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J106" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K106" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="L106" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -22448,19 +22640,19 @@
         <v>533</v>
       </c>
       <c r="G107" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H107" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="J107" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K107" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
       <c r="L107" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -22477,19 +22669,19 @@
         <v>534</v>
       </c>
       <c r="G108" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H108" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J108" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K108" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
       <c r="L108" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -22506,19 +22698,19 @@
         <v>535</v>
       </c>
       <c r="G109" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H109" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J109" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K109" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="L109" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -22535,19 +22727,19 @@
         <v>536</v>
       </c>
       <c r="G110" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H110" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J110" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K110" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="L110" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -22564,19 +22756,19 @@
         <v>537</v>
       </c>
       <c r="G111" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H111" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J111" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K111" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="L111" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -22593,19 +22785,19 @@
         <v>538</v>
       </c>
       <c r="G112" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H112" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="J112" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K112" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="L112" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -22622,19 +22814,19 @@
         <v>539</v>
       </c>
       <c r="G113" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H113" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J113" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K113" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
       <c r="L113" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -22651,19 +22843,19 @@
         <v>540</v>
       </c>
       <c r="G114" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H114" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J114" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K114" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="L114" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -22680,19 +22872,19 @@
         <v>541</v>
       </c>
       <c r="G115" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H115" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J115" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K115" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="L115" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -22709,19 +22901,19 @@
         <v>542</v>
       </c>
       <c r="G116" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H116" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J116" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K116" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="L116" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -22738,19 +22930,19 @@
         <v>543</v>
       </c>
       <c r="G117" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H117" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J117" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K117" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
       <c r="L117" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -22767,19 +22959,19 @@
         <v>544</v>
       </c>
       <c r="G118" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H118" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J118" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K118" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="L118" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -22796,19 +22988,19 @@
         <v>545</v>
       </c>
       <c r="G119" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H119" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J119" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K119" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
       <c r="L119" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -22825,19 +23017,19 @@
         <v>546</v>
       </c>
       <c r="G120" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H120" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J120" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K120" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="L120" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -22854,19 +23046,19 @@
         <v>547</v>
       </c>
       <c r="G121" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H121" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J121" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K121" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="L121" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -22883,19 +23075,19 @@
         <v>548</v>
       </c>
       <c r="G122" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H122" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J122" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K122" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
       <c r="L122" t="s">
-        <v>702</v>
+        <v>718</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -22912,19 +23104,19 @@
         <v>549</v>
       </c>
       <c r="G123" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H123" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J123" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K123" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
       <c r="L123" t="s">
-        <v>703</v>
+        <v>719</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -22941,19 +23133,19 @@
         <v>550</v>
       </c>
       <c r="G124" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H124" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="J124" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K124" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
       <c r="L124" t="s">
-        <v>704</v>
+        <v>720</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -22970,19 +23162,19 @@
         <v>551</v>
       </c>
       <c r="G125" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H125" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J125" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K125" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="L125" t="s">
-        <v>705</v>
+        <v>721</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -22999,19 +23191,19 @@
         <v>552</v>
       </c>
       <c r="G126" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H126" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J126" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K126" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="L126" t="s">
-        <v>706</v>
+        <v>722</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -23028,19 +23220,19 @@
         <v>553</v>
       </c>
       <c r="G127" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H127" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J127" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K127" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
       <c r="L127" t="s">
-        <v>707</v>
+        <v>723</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -23057,19 +23249,19 @@
         <v>554</v>
       </c>
       <c r="G128" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H128" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
       <c r="J128" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K128" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
       <c r="L128" t="s">
-        <v>708</v>
+        <v>724</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -23086,19 +23278,19 @@
         <v>555</v>
       </c>
       <c r="G129" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H129" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="J129" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K129" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
       <c r="L129" t="s">
-        <v>709</v>
+        <v>725</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -23115,19 +23307,19 @@
         <v>556</v>
       </c>
       <c r="G130" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H130" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="J130" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K130" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
       <c r="L130" t="s">
-        <v>710</v>
+        <v>726</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -23144,19 +23336,19 @@
         <v>557</v>
       </c>
       <c r="G131" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H131" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J131" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K131" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
       <c r="L131" t="s">
-        <v>711</v>
+        <v>727</v>
       </c>
     </row>
     <row r="132" spans="2:12">
@@ -23173,19 +23365,19 @@
         <v>558</v>
       </c>
       <c r="G132" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H132" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J132" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K132" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
       <c r="L132" t="s">
-        <v>712</v>
+        <v>728</v>
       </c>
     </row>
     <row r="133" spans="2:12">
@@ -23202,19 +23394,19 @@
         <v>559</v>
       </c>
       <c r="G133" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H133" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="J133" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K133" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
       <c r="L133" t="s">
-        <v>713</v>
+        <v>729</v>
       </c>
     </row>
     <row r="134" spans="2:12">
@@ -23231,19 +23423,19 @@
         <v>560</v>
       </c>
       <c r="G134" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H134" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J134" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K134" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
       <c r="L134" t="s">
-        <v>714</v>
+        <v>730</v>
       </c>
     </row>
     <row r="135" spans="2:12">
@@ -23260,19 +23452,19 @@
         <v>561</v>
       </c>
       <c r="G135" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H135" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J135" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K135" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
       <c r="L135" t="s">
-        <v>715</v>
+        <v>731</v>
       </c>
     </row>
     <row r="136" spans="2:12">
@@ -23289,19 +23481,19 @@
         <v>562</v>
       </c>
       <c r="G136" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H136" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J136" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K136" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
       <c r="L136" t="s">
-        <v>716</v>
+        <v>732</v>
       </c>
     </row>
     <row r="137" spans="2:12">
@@ -23318,19 +23510,19 @@
         <v>563</v>
       </c>
       <c r="G137" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H137" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J137" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K137" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
       <c r="L137" t="s">
-        <v>717</v>
+        <v>733</v>
       </c>
     </row>
     <row r="138" spans="2:12">
@@ -23347,19 +23539,19 @@
         <v>564</v>
       </c>
       <c r="G138" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H138" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="J138" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K138" t="s">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="L138" t="s">
-        <v>718</v>
+        <v>734</v>
       </c>
     </row>
     <row r="139" spans="2:12">
@@ -23376,19 +23568,19 @@
         <v>565</v>
       </c>
       <c r="G139" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H139" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="J139" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K139" t="s">
-        <v>719</v>
+        <v>735</v>
       </c>
       <c r="L139" t="s">
-        <v>719</v>
+        <v>735</v>
       </c>
     </row>
     <row r="140" spans="2:12">
@@ -23405,19 +23597,19 @@
         <v>566</v>
       </c>
       <c r="G140" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H140" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J140" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K140" t="s">
-        <v>720</v>
+        <v>736</v>
       </c>
       <c r="L140" t="s">
-        <v>720</v>
+        <v>736</v>
       </c>
     </row>
     <row r="141" spans="2:12">
@@ -23434,19 +23626,19 @@
         <v>567</v>
       </c>
       <c r="G141" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H141" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J141" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K141" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="L141" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
     </row>
     <row r="142" spans="2:12">
@@ -23463,19 +23655,19 @@
         <v>568</v>
       </c>
       <c r="G142" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H142" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J142" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K142" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="L142" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
     </row>
     <row r="143" spans="2:12">
@@ -23492,19 +23684,19 @@
         <v>569</v>
       </c>
       <c r="G143" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H143" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J143" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K143" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="L143" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
     </row>
     <row r="144" spans="2:12">
@@ -23521,19 +23713,19 @@
         <v>570</v>
       </c>
       <c r="G144" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H144" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J144" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K144" t="s">
-        <v>724</v>
+        <v>740</v>
       </c>
       <c r="L144" t="s">
-        <v>724</v>
+        <v>740</v>
       </c>
     </row>
     <row r="145" spans="2:12">
@@ -23550,19 +23742,19 @@
         <v>571</v>
       </c>
       <c r="G145" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H145" t="s">
-        <v>581</v>
+        <v>604</v>
       </c>
       <c r="J145" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K145" t="s">
-        <v>725</v>
+        <v>741</v>
       </c>
       <c r="L145" t="s">
-        <v>725</v>
+        <v>741</v>
       </c>
     </row>
     <row r="146" spans="2:12">
@@ -23579,19 +23771,19 @@
         <v>572</v>
       </c>
       <c r="G146" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H146" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="J146" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K146" t="s">
-        <v>726</v>
+        <v>742</v>
       </c>
       <c r="L146" t="s">
-        <v>726</v>
+        <v>742</v>
       </c>
     </row>
     <row r="147" spans="2:12">
@@ -23608,19 +23800,19 @@
         <v>573</v>
       </c>
       <c r="G147" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H147" t="s">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="J147" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K147" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
       <c r="L147" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
     </row>
     <row r="148" spans="2:12">
@@ -23637,19 +23829,19 @@
         <v>574</v>
       </c>
       <c r="G148" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H148" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="J148" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K148" t="s">
-        <v>728</v>
+        <v>744</v>
       </c>
       <c r="L148" t="s">
-        <v>728</v>
+        <v>744</v>
       </c>
     </row>
     <row r="149" spans="2:12">
@@ -23666,19 +23858,19 @@
         <v>575</v>
       </c>
       <c r="G149" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H149" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J149" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K149" t="s">
-        <v>729</v>
+        <v>745</v>
       </c>
       <c r="L149" t="s">
-        <v>729</v>
+        <v>745</v>
       </c>
     </row>
     <row r="150" spans="2:12">
@@ -23695,19 +23887,19 @@
         <v>576</v>
       </c>
       <c r="G150" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H150" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J150" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K150" t="s">
-        <v>730</v>
+        <v>746</v>
       </c>
       <c r="L150" t="s">
-        <v>730</v>
+        <v>746</v>
       </c>
     </row>
     <row r="151" spans="2:12">
@@ -23724,19 +23916,19 @@
         <v>577</v>
       </c>
       <c r="G151" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H151" t="s">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="J151" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K151" t="s">
-        <v>731</v>
+        <v>747</v>
       </c>
       <c r="L151" t="s">
-        <v>731</v>
+        <v>747</v>
       </c>
     </row>
     <row r="152" spans="2:12">
@@ -23753,19 +23945,19 @@
         <v>578</v>
       </c>
       <c r="G152" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="H152" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="J152" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K152" t="s">
-        <v>732</v>
+        <v>748</v>
       </c>
       <c r="L152" t="s">
-        <v>732</v>
+        <v>748</v>
       </c>
     </row>
     <row r="153" spans="2:12">
@@ -23782,195 +23974,483 @@
         <v>579</v>
       </c>
       <c r="G153" t="s">
+        <v>596</v>
+      </c>
+      <c r="H153" t="s">
+        <v>598</v>
+      </c>
+      <c r="J153" t="s">
+        <v>606</v>
+      </c>
+      <c r="K153" t="s">
+        <v>749</v>
+      </c>
+      <c r="L153" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="154" spans="2:12">
+      <c r="B154" t="s">
+        <v>436</v>
+      </c>
+      <c r="C154" t="s">
         <v>580</v>
       </c>
-      <c r="H153" t="s">
+      <c r="D154" t="s">
+        <v>580</v>
+      </c>
+      <c r="F154" t="s">
+        <v>580</v>
+      </c>
+      <c r="G154" t="s">
+        <v>596</v>
+      </c>
+      <c r="H154" t="s">
+        <v>603</v>
+      </c>
+      <c r="J154" t="s">
+        <v>606</v>
+      </c>
+      <c r="K154" t="s">
+        <v>750</v>
+      </c>
+      <c r="L154" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="155" spans="2:12">
+      <c r="B155" t="s">
+        <v>436</v>
+      </c>
+      <c r="C155" t="s">
+        <v>581</v>
+      </c>
+      <c r="D155" t="s">
+        <v>581</v>
+      </c>
+      <c r="F155" t="s">
+        <v>581</v>
+      </c>
+      <c r="G155" t="s">
+        <v>596</v>
+      </c>
+      <c r="H155" t="s">
+        <v>597</v>
+      </c>
+      <c r="J155" t="s">
+        <v>606</v>
+      </c>
+      <c r="K155" t="s">
+        <v>751</v>
+      </c>
+      <c r="L155" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="156" spans="2:12">
+      <c r="B156" t="s">
+        <v>436</v>
+      </c>
+      <c r="C156" t="s">
+        <v>582</v>
+      </c>
+      <c r="D156" t="s">
+        <v>582</v>
+      </c>
+      <c r="F156" t="s">
+        <v>582</v>
+      </c>
+      <c r="G156" t="s">
+        <v>596</v>
+      </c>
+      <c r="H156" t="s">
+        <v>597</v>
+      </c>
+      <c r="J156" t="s">
+        <v>606</v>
+      </c>
+      <c r="K156" t="s">
+        <v>752</v>
+      </c>
+      <c r="L156" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="157" spans="2:12">
+      <c r="B157" t="s">
+        <v>436</v>
+      </c>
+      <c r="C157" t="s">
         <v>583</v>
       </c>
-      <c r="J153" t="s">
+      <c r="D157" t="s">
+        <v>583</v>
+      </c>
+      <c r="F157" t="s">
+        <v>583</v>
+      </c>
+      <c r="G157" t="s">
+        <v>596</v>
+      </c>
+      <c r="H157" t="s">
+        <v>597</v>
+      </c>
+      <c r="J157" t="s">
+        <v>606</v>
+      </c>
+      <c r="K157" t="s">
+        <v>753</v>
+      </c>
+      <c r="L157" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="158" spans="2:12">
+      <c r="B158" t="s">
+        <v>436</v>
+      </c>
+      <c r="C158" t="s">
+        <v>584</v>
+      </c>
+      <c r="D158" t="s">
+        <v>584</v>
+      </c>
+      <c r="F158" t="s">
+        <v>584</v>
+      </c>
+      <c r="G158" t="s">
+        <v>596</v>
+      </c>
+      <c r="H158" t="s">
+        <v>597</v>
+      </c>
+      <c r="J158" t="s">
+        <v>606</v>
+      </c>
+      <c r="K158" t="s">
+        <v>754</v>
+      </c>
+      <c r="L158" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="159" spans="2:12">
+      <c r="B159" t="s">
+        <v>436</v>
+      </c>
+      <c r="C159" t="s">
+        <v>585</v>
+      </c>
+      <c r="D159" t="s">
+        <v>585</v>
+      </c>
+      <c r="F159" t="s">
+        <v>585</v>
+      </c>
+      <c r="G159" t="s">
+        <v>596</v>
+      </c>
+      <c r="H159" t="s">
+        <v>597</v>
+      </c>
+      <c r="J159" t="s">
+        <v>606</v>
+      </c>
+      <c r="K159" t="s">
+        <v>755</v>
+      </c>
+      <c r="L159" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12">
+      <c r="B160" t="s">
+        <v>436</v>
+      </c>
+      <c r="C160" t="s">
+        <v>586</v>
+      </c>
+      <c r="D160" t="s">
+        <v>586</v>
+      </c>
+      <c r="F160" t="s">
+        <v>586</v>
+      </c>
+      <c r="G160" t="s">
+        <v>596</v>
+      </c>
+      <c r="H160" t="s">
+        <v>597</v>
+      </c>
+      <c r="J160" t="s">
+        <v>606</v>
+      </c>
+      <c r="K160" t="s">
+        <v>756</v>
+      </c>
+      <c r="L160" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="161" spans="2:12">
+      <c r="B161" t="s">
+        <v>436</v>
+      </c>
+      <c r="C161" t="s">
+        <v>587</v>
+      </c>
+      <c r="D161" t="s">
+        <v>587</v>
+      </c>
+      <c r="F161" t="s">
+        <v>587</v>
+      </c>
+      <c r="G161" t="s">
+        <v>596</v>
+      </c>
+      <c r="H161" t="s">
+        <v>597</v>
+      </c>
+      <c r="J161" t="s">
+        <v>606</v>
+      </c>
+      <c r="K161" t="s">
+        <v>757</v>
+      </c>
+      <c r="L161" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="162" spans="2:12">
+      <c r="B162" t="s">
+        <v>436</v>
+      </c>
+      <c r="C162" t="s">
+        <v>588</v>
+      </c>
+      <c r="D162" t="s">
+        <v>588</v>
+      </c>
+      <c r="F162" t="s">
+        <v>588</v>
+      </c>
+      <c r="G162" t="s">
+        <v>596</v>
+      </c>
+      <c r="H162" t="s">
+        <v>597</v>
+      </c>
+      <c r="J162" t="s">
+        <v>606</v>
+      </c>
+      <c r="K162" t="s">
+        <v>758</v>
+      </c>
+      <c r="L162" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="163" spans="2:12">
+      <c r="B163" t="s">
+        <v>436</v>
+      </c>
+      <c r="C163" t="s">
+        <v>589</v>
+      </c>
+      <c r="D163" t="s">
+        <v>589</v>
+      </c>
+      <c r="F163" t="s">
+        <v>589</v>
+      </c>
+      <c r="G163" t="s">
+        <v>596</v>
+      </c>
+      <c r="H163" t="s">
+        <v>600</v>
+      </c>
+      <c r="J163" t="s">
+        <v>606</v>
+      </c>
+      <c r="K163" t="s">
+        <v>759</v>
+      </c>
+      <c r="L163" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="164" spans="2:12">
+      <c r="B164" t="s">
+        <v>436</v>
+      </c>
+      <c r="C164" t="s">
         <v>590</v>
       </c>
-      <c r="K153" t="s">
-        <v>733</v>
-      </c>
-      <c r="L153" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="154" spans="2:12">
-      <c r="J154" t="s">
+      <c r="D164" t="s">
         <v>590</v>
       </c>
-      <c r="K154" t="s">
-        <v>734</v>
-      </c>
-      <c r="L154" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="155" spans="2:12">
-      <c r="J155" t="s">
+      <c r="F164" t="s">
         <v>590</v>
       </c>
-      <c r="K155" t="s">
-        <v>735</v>
-      </c>
-      <c r="L155" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="156" spans="2:12">
-      <c r="J156" t="s">
-        <v>590</v>
-      </c>
-      <c r="K156" t="s">
-        <v>736</v>
-      </c>
-      <c r="L156" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="157" spans="2:12">
-      <c r="J157" t="s">
-        <v>590</v>
-      </c>
-      <c r="K157" t="s">
-        <v>737</v>
-      </c>
-      <c r="L157" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="158" spans="2:12">
-      <c r="J158" t="s">
-        <v>590</v>
-      </c>
-      <c r="K158" t="s">
-        <v>738</v>
-      </c>
-      <c r="L158" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="159" spans="2:12">
-      <c r="J159" t="s">
-        <v>590</v>
-      </c>
-      <c r="K159" t="s">
-        <v>739</v>
-      </c>
-      <c r="L159" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="160" spans="2:12">
-      <c r="J160" t="s">
-        <v>590</v>
-      </c>
-      <c r="K160" t="s">
-        <v>740</v>
-      </c>
-      <c r="L160" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="161" spans="10:12">
-      <c r="J161" t="s">
-        <v>590</v>
-      </c>
-      <c r="K161" t="s">
-        <v>741</v>
-      </c>
-      <c r="L161" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="162" spans="10:12">
-      <c r="J162" t="s">
-        <v>590</v>
-      </c>
-      <c r="K162" t="s">
-        <v>742</v>
-      </c>
-      <c r="L162" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="163" spans="10:12">
-      <c r="J163" t="s">
-        <v>590</v>
-      </c>
-      <c r="K163" t="s">
-        <v>743</v>
-      </c>
-      <c r="L163" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="164" spans="10:12">
+      <c r="G164" t="s">
+        <v>596</v>
+      </c>
+      <c r="H164" t="s">
+        <v>598</v>
+      </c>
       <c r="J164" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K164" t="s">
-        <v>744</v>
+        <v>760</v>
       </c>
       <c r="L164" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="165" spans="10:12">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="165" spans="2:12">
+      <c r="B165" t="s">
+        <v>436</v>
+      </c>
+      <c r="C165" t="s">
+        <v>591</v>
+      </c>
+      <c r="D165" t="s">
+        <v>591</v>
+      </c>
+      <c r="F165" t="s">
+        <v>591</v>
+      </c>
+      <c r="G165" t="s">
+        <v>596</v>
+      </c>
+      <c r="H165" t="s">
+        <v>604</v>
+      </c>
       <c r="J165" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K165" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
       <c r="L165" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="166" spans="10:12">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="166" spans="2:12">
+      <c r="B166" t="s">
+        <v>436</v>
+      </c>
+      <c r="C166" t="s">
+        <v>592</v>
+      </c>
+      <c r="D166" t="s">
+        <v>592</v>
+      </c>
+      <c r="F166" t="s">
+        <v>592</v>
+      </c>
+      <c r="G166" t="s">
+        <v>596</v>
+      </c>
+      <c r="H166" t="s">
+        <v>597</v>
+      </c>
       <c r="J166" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K166" t="s">
-        <v>746</v>
+        <v>762</v>
       </c>
       <c r="L166" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="167" spans="10:12">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="167" spans="2:12">
+      <c r="B167" t="s">
+        <v>436</v>
+      </c>
+      <c r="C167" t="s">
+        <v>593</v>
+      </c>
+      <c r="D167" t="s">
+        <v>593</v>
+      </c>
+      <c r="F167" t="s">
+        <v>593</v>
+      </c>
+      <c r="G167" t="s">
+        <v>596</v>
+      </c>
+      <c r="H167" t="s">
+        <v>597</v>
+      </c>
       <c r="J167" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K167" t="s">
-        <v>747</v>
+        <v>763</v>
       </c>
       <c r="L167" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="168" spans="10:12">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="168" spans="2:12">
+      <c r="B168" t="s">
+        <v>436</v>
+      </c>
+      <c r="C168" t="s">
+        <v>594</v>
+      </c>
+      <c r="D168" t="s">
+        <v>594</v>
+      </c>
+      <c r="F168" t="s">
+        <v>594</v>
+      </c>
+      <c r="G168" t="s">
+        <v>596</v>
+      </c>
+      <c r="H168" t="s">
+        <v>599</v>
+      </c>
       <c r="J168" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K168" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="L168" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="169" spans="10:12">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="169" spans="2:12">
+      <c r="B169" t="s">
+        <v>436</v>
+      </c>
+      <c r="C169" t="s">
+        <v>595</v>
+      </c>
+      <c r="D169" t="s">
+        <v>595</v>
+      </c>
+      <c r="F169" t="s">
+        <v>595</v>
+      </c>
+      <c r="G169" t="s">
+        <v>596</v>
+      </c>
+      <c r="H169" t="s">
+        <v>599</v>
+      </c>
       <c r="J169" t="s">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="K169" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="L169" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A4BE810-F055-4AEC-B65E-EFC9C7A972D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E562AA1F-9492-41A9-8FD2-1BC1C859C6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3409,7 +3409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3178FF-8CED-46E8-9658-1BE80596FCC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80696747-537C-48D3-97CD-0318089DEE9E}">
   <dimension ref="B9:H169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -19798,7 +19798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6122EEEE-5A41-4998-8599-47D862430E5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21447089-8D33-4793-860F-146478A2F496}">
   <dimension ref="B9:L169"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ARE_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE84E610-76CF-4786-829C-8504EC568FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A1A66-1495-4F9F-9BB0-C3865E959CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5338" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5343" uniqueCount="922">
   <si>
     <t>Unit</t>
   </si>
@@ -26316,7 +26316,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -26496,16 +26496,21 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>118</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="G7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I7" s="2"/>
       <c r="K7" t="s">
-        <v>120</v>
+        <v>314</v>
       </c>
       <c r="N7" t="s">
-        <v>122</v>
+        <v>37</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>111</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -26515,37 +26520,36 @@
         <v>4</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>307</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>110</v>
+        <v>4</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="K9" t="s">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C10" t="s">
         <v>108</v>
@@ -26562,7 +26566,7 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C11" t="s">
         <v>108</v>
@@ -26574,12 +26578,12 @@
         <v>254</v>
       </c>
       <c r="N11" t="s">
-        <v>301</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
@@ -26596,7 +26600,7 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C13" t="s">
         <v>108</v>
@@ -26608,48 +26612,42 @@
         <v>254</v>
       </c>
       <c r="N13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C14" t="s">
-        <v>304</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="I14" t="s">
-        <v>305</v>
+        <v>108</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="K14" t="s">
         <v>254</v>
       </c>
       <c r="N14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="I15" t="s">
+        <v>305</v>
+      </c>
+      <c r="K15" t="s">
+        <v>254</v>
+      </c>
+      <c r="N15" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>315</v>
-      </c>
-      <c r="N15" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -26659,98 +26657,104 @@
       <c r="B16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I16" t="s">
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>315</v>
+      </c>
+      <c r="N16" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" t="s">
         <v>130</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K17" t="s">
         <v>131</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
+    <row r="18" spans="1:17">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K18" t="s">
         <v>77</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N18" t="s">
         <v>44</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P18" t="s">
         <v>46</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="Q18" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" t="s">
-        <v>315</v>
-      </c>
-      <c r="N18" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="4" t="s">
-        <v>252</v>
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="K19" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
       <c r="N19" t="s">
-        <v>255</v>
+        <v>56</v>
       </c>
       <c r="Q19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K20" t="s">
         <v>254</v>
       </c>
       <c r="N20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" t="s">
-        <v>266</v>
-      </c>
-      <c r="D21" t="s">
-        <v>267</v>
+      <c r="A21" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="K21" t="s">
-        <v>7</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s">
-        <v>268</v>
+        <v>256</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
         <v>266</v>
@@ -26762,49 +26766,46 @@
         <v>7</v>
       </c>
       <c r="N22" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" t="s">
+        <v>267</v>
+      </c>
+      <c r="K23" t="s">
+        <v>7</v>
+      </c>
+      <c r="N23" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
-      <c r="A23" s="4" t="s">
+    <row r="24" spans="1:17">
+      <c r="A24" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>916</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I24" t="s">
         <v>275</v>
-      </c>
-      <c r="K23" t="s">
-        <v>141</v>
-      </c>
-      <c r="N23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" t="s">
-        <v>142</v>
-      </c>
-      <c r="I24" t="s">
-        <v>277</v>
       </c>
       <c r="K24" t="s">
         <v>141</v>
       </c>
       <c r="N24" t="s">
-        <v>295</v>
-      </c>
-      <c r="P24" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>276</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="I25" t="s">
         <v>277</v>
@@ -26813,7 +26814,7 @@
         <v>141</v>
       </c>
       <c r="N25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P25" t="s">
         <v>292</v>
@@ -26824,30 +26825,27 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>299</v>
-      </c>
-      <c r="G26" t="s">
-        <v>299</v>
+        <v>4</v>
+      </c>
+      <c r="I26" t="s">
+        <v>277</v>
       </c>
       <c r="K26" t="s">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="N26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q26" t="s">
-        <v>39</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>299</v>
@@ -26859,12 +26857,35 @@
         <v>7</v>
       </c>
       <c r="N27" t="s">
+        <v>297</v>
+      </c>
+      <c r="P27" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" t="s">
+        <v>299</v>
+      </c>
+      <c r="G28" t="s">
+        <v>299</v>
+      </c>
+      <c r="K28" t="s">
+        <v>7</v>
+      </c>
+      <c r="N28" t="s">
         <v>298</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P28" t="s">
         <v>294</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="Q28" t="s">
         <v>39</v>
       </c>
     </row>

--- a/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_ARE_grids_kan/ReportDefs_vervestacks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A1A66-1495-4F9F-9BB0-C3865E959CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8FBAA9-3A0D-44D9-880B-607528B3475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5343" uniqueCount="922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5346" uniqueCount="924">
   <si>
     <t>Unit</t>
   </si>
@@ -2849,6 +2849,12 @@
   </si>
   <si>
     <t>ELE,STG,IRE,DMD</t>
+  </si>
+  <si>
+    <t>e_stargate</t>
+  </si>
+  <si>
+    <t>Stargate</t>
   </si>
 </sst>
 </file>
@@ -6950,7 +6956,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -7656,10 +7662,10 @@
         <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>922</v>
       </c>
       <c r="C58" t="s">
-        <v>91</v>
+        <v>923</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -7667,21 +7673,21 @@
         <v>270</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C59" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="C60" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -7689,10 +7695,10 @@
         <v>279</v>
       </c>
       <c r="B61" t="s">
-        <v>280</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -7700,10 +7706,10 @@
         <v>279</v>
       </c>
       <c r="B62" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C62" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -7711,10 +7717,10 @@
         <v>279</v>
       </c>
       <c r="B63" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C63" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7722,10 +7728,10 @@
         <v>279</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C64" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -7733,10 +7739,10 @@
         <v>279</v>
       </c>
       <c r="B65" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C65" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -7744,22 +7750,21 @@
         <v>279</v>
       </c>
       <c r="B66" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C66" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>300</v>
-      </c>
-      <c r="C67" t="str">
-        <f>E67</f>
-        <v>bioenergy</v>
-      </c>
-      <c r="E67" t="s">
-        <v>165</v>
+        <v>279</v>
+      </c>
+      <c r="B67" t="s">
+        <v>290</v>
+      </c>
+      <c r="C67" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -7767,11 +7772,11 @@
         <v>300</v>
       </c>
       <c r="C68" t="str">
-        <f t="shared" ref="C68:C75" si="1">E68</f>
-        <v>coal</v>
+        <f>E68</f>
+        <v>bioenergy</v>
       </c>
       <c r="E68" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -7779,11 +7784,11 @@
         <v>300</v>
       </c>
       <c r="C69" t="str">
-        <f t="shared" si="1"/>
-        <v>gas</v>
+        <f t="shared" ref="C69:C76" si="1">E69</f>
+        <v>coal</v>
       </c>
       <c r="E69" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -7792,10 +7797,10 @@
       </c>
       <c r="C70" t="str">
         <f t="shared" si="1"/>
-        <v>hydro</v>
+        <v>gas</v>
       </c>
       <c r="E70" t="s">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -7804,10 +7809,10 @@
       </c>
       <c r="C71" t="str">
         <f t="shared" si="1"/>
-        <v>nuclear</v>
+        <v>hydro</v>
       </c>
       <c r="E71" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -7816,10 +7821,10 @@
       </c>
       <c r="C72" t="str">
         <f t="shared" si="1"/>
-        <v>oil</v>
+        <v>nuclear</v>
       </c>
       <c r="E72" t="s">
-        <v>230</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -7828,10 +7833,10 @@
       </c>
       <c r="C73" t="str">
         <f t="shared" si="1"/>
-        <v>solar</v>
+        <v>oil</v>
       </c>
       <c r="E73" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -7840,10 +7845,10 @@
       </c>
       <c r="C74" t="str">
         <f t="shared" si="1"/>
-        <v>windoff</v>
+        <v>solar</v>
       </c>
       <c r="E74" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -7852,9 +7857,21 @@
       </c>
       <c r="C75" t="str">
         <f t="shared" si="1"/>
+        <v>windoff</v>
+      </c>
+      <c r="E75" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="1"/>
         <v>windon</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E76" t="s">
         <v>232</v>
       </c>
     </row>
